--- a/STUDIO/org.openl.rules.test/test-resources/functionality/EPBDS-13565_Access_to_table_properties/propertyAccessTest.xlsx
+++ b/STUDIO/org.openl.rules.test/test-resources/functionality/EPBDS-13565_Access_to_table_properties/propertyAccessTest.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="392">
   <si>
     <t>Spreadsheet  SpreadsheetResult mySpreadsheetWithProperties()</t>
   </si>
@@ -49,9 +49,6 @@
     <t>QC,HQ</t>
   </si>
   <si>
-    <t>cacheable</t>
-  </si>
-  <si>
     <t>category</t>
   </si>
   <si>
@@ -253,18 +250,6 @@
     <t>=$dispatchingProperties.caRegions[2]</t>
   </si>
   <si>
-    <t>Cacheable</t>
-  </si>
-  <si>
-    <t>=$properties.cacheable</t>
-  </si>
-  <si>
-    <t>=$dispatchingProperties.cacheable[1]</t>
-  </si>
-  <si>
-    <t>=$dispatchingProperties.cacheable[2]</t>
-  </si>
-  <si>
     <t>Category</t>
   </si>
   <si>
@@ -508,19 +493,19 @@
     <t>ReturnObject</t>
   </si>
   <si>
-    <t>=SpreadsheetProperties($Properties$CalculateAllCells, $Properties$AutoType, $Properties$TableStructureDetails, $Properties$BuildPhase, $Properties$CaProvinces, $Properties$CaRegions, $Properties$Cacheable, $Properties$Category, $Properties$Country, $Properties$Currency, $Properties$Description, $Properties$EffectiveDate, setTime($Properties$EndRequestDate,0,0,0,0), setTime($Properties$ExpirationDate,0,0,0,0), $Properties$Id, $Properties$Lang, $Properties$Lob, $Properties$Nature, $Properties$Origin, $Properties$Parallel, $Properties$Region, $Properties$StartRequestDate, $Properties$State, $Properties$Tags, $Properties$Usregion, $Properties$Version, $Properties$Active)</t>
-  </si>
-  <si>
-    <t>=SpreadsheetProperties($DispatchingProperties$CalculateAllCells, $DispatchingProperties$AutoType, $DispatchingProperties$TableStructureDetails, $DispatchingProperties$BuildPhase, $DispatchingProperties$CaProvinces, $DispatchingProperties$CaRegions, $DispatchingProperties$Cacheable, $DispatchingProperties$Category, $DispatchingProperties$Country, $DispatchingProperties$Currency, $DispatchingProperties$Description, $DispatchingProperties$EffectiveDate, setTime($DispatchingProperties$EndRequestDate,0,0,0,0), setTime($DispatchingProperties$ExpirationDate,0,0,0,0), $DispatchingProperties$Id, $DispatchingProperties$Lang, $DispatchingProperties$Lob, $DispatchingProperties$Nature, $DispatchingProperties$Origin, $DispatchingProperties$Parallel, $DispatchingProperties$Region, $DispatchingProperties$StartRequestDate, $DispatchingProperties$State, $DispatchingProperties$Tags, $DispatchingProperties$Usregion, $DispatchingProperties$Version, $DispatchingProperties$Active)</t>
-  </si>
-  <si>
-    <t>=SpreadsheetProperties($AnotherFileTable$CalculateAllCells, $AnotherFileTable$AutoType, $AnotherFileTable$TableStructureDetails, $AnotherFileTable$BuildPhase, $AnotherFileTable$CaProvinces, $AnotherFileTable$CaRegions, $AnotherFileTable$Cacheable, $AnotherFileTable$Category, $AnotherFileTable$Country, $AnotherFileTable$Currency, $AnotherFileTable$Description, $AnotherFileTable$EffectiveDate, setTime($AnotherFileTable$EndRequestDate,0,0,0,0), setTime($AnotherFileTable$ExpirationDate,0,0,0,0), $AnotherFileTable$Id, $AnotherFileTable$Lang, $AnotherFileTable$Lob, $AnotherFileTable$Nature, $AnotherFileTable$Origin, $AnotherFileTable$Parallel, $AnotherFileTable$Region, $AnotherFileTable$StartRequestDate, $AnotherFileTable$State, $AnotherFileTable$Tags, $AnotherFileTable$Usregion, $AnotherFileTable$Version, $AnotherFileTable$Active)</t>
+    <t>=SpreadsheetProperties($Properties$CalculateAllCells, $Properties$AutoType, $Properties$TableStructureDetails, $Properties$BuildPhase, $Properties$CaProvinces, $Properties$CaRegions, $Properties$Category, $Properties$Country, $Properties$Currency, $Properties$Description, $Properties$EffectiveDate, setTime($Properties$EndRequestDate,0,0,0,0), setTime($Properties$ExpirationDate,0,0,0,0), $Properties$Id, $Properties$Lang, $Properties$Lob, $Properties$Nature, $Properties$Origin, $Properties$Parallel, $Properties$Region, $Properties$StartRequestDate, $Properties$State, $Properties$Tags, $Properties$Usregion, $Properties$Version, $Properties$Active)</t>
+  </si>
+  <si>
+    <t>=SpreadsheetProperties($DispatchingProperties$CalculateAllCells, $DispatchingProperties$AutoType, $DispatchingProperties$TableStructureDetails, $DispatchingProperties$BuildPhase, $DispatchingProperties$CaProvinces, $DispatchingProperties$CaRegions, $DispatchingProperties$Category, $DispatchingProperties$Country, $DispatchingProperties$Currency, $DispatchingProperties$Description, $DispatchingProperties$EffectiveDate, setTime($DispatchingProperties$EndRequestDate,0,0,0,0), setTime($DispatchingProperties$ExpirationDate,0,0,0,0), $DispatchingProperties$Id, $DispatchingProperties$Lang, $DispatchingProperties$Lob, $DispatchingProperties$Nature, $DispatchingProperties$Origin, $DispatchingProperties$Parallel, $DispatchingProperties$Region, $DispatchingProperties$StartRequestDate, $DispatchingProperties$State, $DispatchingProperties$Tags, $DispatchingProperties$Usregion, $DispatchingProperties$Version, $DispatchingProperties$Active)</t>
+  </si>
+  <si>
+    <t>=SpreadsheetProperties($AnotherFileTable$CalculateAllCells, $AnotherFileTable$AutoType, $AnotherFileTable$TableStructureDetails, $AnotherFileTable$BuildPhase, $AnotherFileTable$CaProvinces, $AnotherFileTable$CaRegions, $AnotherFileTable$Category, $AnotherFileTable$Country, $AnotherFileTable$Currency, $AnotherFileTable$Description, $AnotherFileTable$EffectiveDate, setTime($AnotherFileTable$EndRequestDate,0,0,0,0), setTime($AnotherFileTable$ExpirationDate,0,0,0,0), $AnotherFileTable$Id, $AnotherFileTable$Lang, $AnotherFileTable$Lob, $AnotherFileTable$Nature, $AnotherFileTable$Origin, $AnotherFileTable$Parallel, $AnotherFileTable$Region, $AnotherFileTable$StartRequestDate, $AnotherFileTable$State, $AnotherFileTable$Tags, $AnotherFileTable$Usregion, $AnotherFileTable$Version, $AnotherFileTable$Active)</t>
   </si>
   <si>
     <t>RetunrnObject</t>
   </si>
   <si>
-    <t>=SpreadsheetProperties($CalculateAllCells, $AutoType, $TableStructureDetails, $BuildPhase, $CaProvinces, $CaRegions, $Cacheable, $Category, $Country, $Currency, $Description, $EffectiveDate, setTime($EndRequestDate,0,0,0,0), setTime($ExpirationDate,0,0,0,0), $Id, $Lang, $Lob, $Nature, $Origin, $Parallel, $Region, $StartRequestDate, $State, $Tags, $Usregion, $Version, $Active)</t>
+    <t>=SpreadsheetProperties($CalculateAllCells, $AutoType, $TableStructureDetails, $BuildPhase, $CaProvinces, $CaRegions, $Category, $Country, $Currency, $Description, $EffectiveDate, setTime($EndRequestDate,0,0,0,0), setTime($ExpirationDate,0,0,0,0), $Id, $Lang, $Lob, $Nature, $Origin, $Parallel, $Region, $StartRequestDate, $State, $Tags, $Usregion, $Version, $Active)</t>
   </si>
   <si>
     <t>special</t>
@@ -592,12 +577,6 @@
     <t>QC, HQ</t>
   </si>
   <si>
-    <t>_res_.$Properties$ReturnObject.cacheable</t>
-  </si>
-  <si>
-    <t>properties cacheable</t>
-  </si>
-  <si>
     <t>_res_.$Properties$ReturnObject.category</t>
   </si>
   <si>
@@ -775,12 +754,6 @@
     <t>dispatching pr   caRegions</t>
   </si>
   <si>
-    <t>_res_.$DispatchingProperties$ReturnObject.cacheable</t>
-  </si>
-  <si>
-    <t>dispatching pr   cacheable</t>
-  </si>
-  <si>
     <t>_res_.$DispatchingProperties$ReturnObject.category</t>
   </si>
   <si>
@@ -958,7 +931,7 @@
     <t>someParam</t>
   </si>
   <si>
-    <t>new RulesProperties($properties.failOnMiss, $properties.cacheable, $properties.emptyResultProcessing, $properties.parallel, $properties.validateDT, $properties.buildPhase, $properties.id, $properties.state, $properties.effectiveDate,$dispatchingProperties[1].failOnMiss, $dispatchingProperties[1].cacheable, $dispatchingProperties[1].emptyResultProcessing, $dispatchingProperties[1].parallel, $dispatchingProperties[1].validateDT, $dispatchingProperties[1].buildPhase, $dispatchingProperties[1].id, $dispatchingProperties[1].state, $dispatchingProperties[1].effectiveDate,$dispatchingProperties[0].failOnMiss, $dispatchingProperties[0].cacheable, $dispatchingProperties[0].emptyResultProcessing, $dispatchingProperties[0].parallel, $dispatchingProperties[0].validateDT, $dispatchingProperties[0].buildPhase, $dispatchingProperties[0].id, $dispatchingProperties[0].state, $dispatchingProperties[0].effectiveDate)</t>
+    <t>new RulesProperties($properties.failOnMiss, $properties.emptyResultProcessing, $properties.parallel, $properties.validateDT, $properties.buildPhase, $properties.id, $properties.state, $properties.effectiveDate,$dispatchingProperties[1].failOnMiss, $dispatchingProperties[1].emptyResultProcessing, $dispatchingProperties[1].parallel, $dispatchingProperties[1].validateDT, $dispatchingProperties[1].buildPhase, $dispatchingProperties[1].id, $dispatchingProperties[1].state, $dispatchingProperties[1].effectiveDate,$dispatchingProperties[0].failOnMiss, $dispatchingProperties[0].emptyResultProcessing, $dispatchingProperties[0].parallel, $dispatchingProperties[0].validateDT, $dispatchingProperties[0].buildPhase, $dispatchingProperties[0].id, $dispatchingProperties[0].state, $dispatchingProperties[0].effectiveDate)</t>
   </si>
   <si>
     <t>Integer</t>
@@ -985,12 +958,6 @@
     <t>failOnMissLocal</t>
   </si>
   <si>
-    <t>_res_.cacheableLocal</t>
-  </si>
-  <si>
-    <t>cacheableLocal</t>
-  </si>
-  <si>
     <t>_res_.emptyResultProcessingLocal</t>
   </si>
   <si>
@@ -1039,12 +1006,6 @@
     <t>failOnMissOtherTable</t>
   </si>
   <si>
-    <t>_res_.cacheableOtherTable</t>
-  </si>
-  <si>
-    <t>cacheableOtherTable</t>
-  </si>
-  <si>
     <t>_res_.emptyResultProcessingOtherTable</t>
   </si>
   <si>
@@ -1094,12 +1055,6 @@
   </si>
   <si>
     <t>failOnMissOtherModule</t>
-  </si>
-  <si>
-    <t>_res_.cacheableOtherModule</t>
-  </si>
-  <si>
-    <t>cacheableOtherModule</t>
   </si>
   <si>
     <t>_res_.emptyResultProcessingOtherModule</t>
@@ -1259,7 +1214,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color indexed="10"/>
+      <color indexed="9"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1269,6 +1224,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="9"/>
+        <bgColor auto="1"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1312,12 +1273,6 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="10"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="26">
     <border>
@@ -1329,41 +1284,41 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
         <color indexed="8"/>
@@ -1372,16 +1327,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
         <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1418,10 +1373,10 @@
         <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1494,10 +1449,10 @@
         <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1506,7 +1461,7 @@
         <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
         <color indexed="8"/>
@@ -1518,7 +1473,7 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
         <color indexed="8"/>
@@ -1542,7 +1497,7 @@
         <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1551,28 +1506,28 @@
         <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
         <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
         <color indexed="8"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1581,22 +1536,22 @@
         <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top/>
       <bottom style="thin">
@@ -1609,10 +1564,10 @@
         <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
         <color indexed="8"/>
@@ -1662,179 +1617,182 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="3" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="14" fontId="0" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="14" fontId="0" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="8" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="15" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="23" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="25" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -1854,8 +1812,8 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffd8d8d8"/>
       <rgbColor rgb="ff8eaadb"/>
       <rgbColor rgb="fffff2cb"/>
@@ -2060,17 +2018,17 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -2098,10 +2056,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -2349,12 +2307,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -2641,7 +2599,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -2669,10 +2627,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -2923,7 +2881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I214"/>
+  <dimension ref="A1:I206"/>
   <sheetFormatPr defaultColWidth="10.8333" defaultRowHeight="16" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="10.8516" style="1" customWidth="1"/>
@@ -3106,97 +3064,97 @@
     </row>
     <row r="11" ht="15.35" customHeight="1">
       <c r="A11" s="5"/>
-      <c r="B11" s="16"/>
+      <c r="B11" s="17"/>
       <c r="C11" t="s" s="13">
         <v>12</v>
       </c>
-      <c r="D11" t="b" s="14">
-        <v>1</v>
+      <c r="D11" t="s" s="13">
+        <v>13</v>
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="9"/>
-      <c r="G11" s="16"/>
+      <c r="G11" s="17"/>
       <c r="H11" t="s" s="13">
         <v>12</v>
       </c>
-      <c r="I11" t="b" s="14">
-        <v>1</v>
+      <c r="I11" t="s" s="13">
+        <v>14</v>
       </c>
     </row>
     <row r="12" ht="15.35" customHeight="1">
       <c r="A12" s="5"/>
       <c r="B12" s="16"/>
       <c r="C12" t="s" s="13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s" s="13">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="9"/>
       <c r="G12" s="16"/>
       <c r="H12" t="s" s="13">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I12" t="s" s="13">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" ht="15.35" customHeight="1">
       <c r="A13" s="5"/>
       <c r="B13" s="16"/>
       <c r="C13" t="s" s="13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13" t="s" s="13">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E13" s="15"/>
       <c r="F13" s="9"/>
       <c r="G13" s="16"/>
       <c r="H13" t="s" s="13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I13" t="s" s="13">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" ht="15.35" customHeight="1">
       <c r="A14" s="5"/>
       <c r="B14" s="16"/>
       <c r="C14" t="s" s="13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" t="s" s="13">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E14" s="15"/>
       <c r="F14" s="9"/>
       <c r="G14" s="16"/>
       <c r="H14" t="s" s="13">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I14" t="s" s="13">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" ht="15.35" customHeight="1">
       <c r="A15" s="5"/>
       <c r="B15" s="16"/>
       <c r="C15" t="s" s="13">
-        <v>20</v>
-      </c>
-      <c r="D15" t="s" s="13">
-        <v>21</v>
-      </c>
-      <c r="E15" s="15"/>
+        <v>22</v>
+      </c>
+      <c r="D15" s="18">
+        <v>45002</v>
+      </c>
+      <c r="E15" s="19"/>
       <c r="F15" s="9"/>
       <c r="G15" s="16"/>
       <c r="H15" t="s" s="13">
-        <v>20</v>
-      </c>
-      <c r="I15" t="s" s="13">
         <v>22</v>
+      </c>
+      <c r="I15" s="18">
+        <v>44621</v>
       </c>
     </row>
     <row r="16" ht="15.35" customHeight="1">
@@ -3205,17 +3163,17 @@
       <c r="C16" t="s" s="13">
         <v>23</v>
       </c>
-      <c r="D16" s="17">
-        <v>45002</v>
-      </c>
-      <c r="E16" s="18"/>
+      <c r="D16" s="18">
+        <v>45172</v>
+      </c>
+      <c r="E16" s="19"/>
       <c r="F16" s="9"/>
       <c r="G16" s="16"/>
       <c r="H16" t="s" s="13">
         <v>23</v>
       </c>
-      <c r="I16" s="17">
-        <v>44621</v>
+      <c r="I16" s="18">
+        <v>44629.999305555553</v>
       </c>
     </row>
     <row r="17" ht="15.35" customHeight="1">
@@ -3224,17 +3182,17 @@
       <c r="C17" t="s" s="13">
         <v>24</v>
       </c>
-      <c r="D17" s="17">
-        <v>45172</v>
-      </c>
-      <c r="E17" s="18"/>
+      <c r="D17" s="18">
+        <v>44993</v>
+      </c>
+      <c r="E17" s="19"/>
       <c r="F17" s="9"/>
       <c r="G17" s="16"/>
       <c r="H17" t="s" s="13">
         <v>24</v>
       </c>
-      <c r="I17" s="17">
-        <v>44629.999305555553</v>
+      <c r="I17" s="18">
+        <v>44628.999305555553</v>
       </c>
     </row>
     <row r="18" ht="15.35" customHeight="1">
@@ -3243,112 +3201,112 @@
       <c r="C18" t="s" s="13">
         <v>25</v>
       </c>
-      <c r="D18" s="17">
-        <v>44993</v>
-      </c>
-      <c r="E18" s="18"/>
+      <c r="D18" t="s" s="13">
+        <v>26</v>
+      </c>
+      <c r="E18" s="15"/>
       <c r="F18" s="9"/>
       <c r="G18" s="16"/>
       <c r="H18" t="s" s="13">
         <v>25</v>
       </c>
-      <c r="I18" s="17">
-        <v>44628.999305555553</v>
+      <c r="I18" t="s" s="13">
+        <v>27</v>
       </c>
     </row>
     <row r="19" ht="15.35" customHeight="1">
       <c r="A19" s="5"/>
       <c r="B19" s="16"/>
       <c r="C19" t="s" s="13">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D19" t="s" s="13">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E19" s="15"/>
       <c r="F19" s="9"/>
       <c r="G19" s="16"/>
       <c r="H19" t="s" s="13">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I19" t="s" s="13">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" ht="15.35" customHeight="1">
       <c r="A20" s="5"/>
       <c r="B20" s="16"/>
       <c r="C20" t="s" s="13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s" s="13">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E20" s="15"/>
       <c r="F20" s="9"/>
       <c r="G20" s="16"/>
       <c r="H20" t="s" s="13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I20" t="s" s="13">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" ht="15.35" customHeight="1">
       <c r="A21" s="5"/>
       <c r="B21" s="16"/>
       <c r="C21" t="s" s="13">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D21" t="s" s="13">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E21" s="15"/>
       <c r="F21" s="9"/>
       <c r="G21" s="16"/>
       <c r="H21" t="s" s="13">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" t="s" s="13">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" ht="15.35" customHeight="1">
       <c r="A22" s="5"/>
       <c r="B22" s="16"/>
       <c r="C22" t="s" s="13">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s" s="13">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E22" s="15"/>
       <c r="F22" s="9"/>
       <c r="G22" s="16"/>
       <c r="H22" t="s" s="13">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I22" t="s" s="13">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" ht="15.35" customHeight="1">
       <c r="A23" s="5"/>
       <c r="B23" s="16"/>
       <c r="C23" t="s" s="13">
-        <v>35</v>
-      </c>
-      <c r="D23" t="s" s="13">
         <v>36</v>
+      </c>
+      <c r="D23" t="b" s="14">
+        <v>1</v>
       </c>
       <c r="E23" s="15"/>
       <c r="F23" s="9"/>
       <c r="G23" s="16"/>
       <c r="H23" t="s" s="13">
-        <v>35</v>
-      </c>
-      <c r="I23" t="s" s="13">
         <v>36</v>
+      </c>
+      <c r="I23" t="b" s="14">
+        <v>1</v>
       </c>
     </row>
     <row r="24" ht="15.35" customHeight="1">
@@ -3357,8 +3315,8 @@
       <c r="C24" t="s" s="13">
         <v>37</v>
       </c>
-      <c r="D24" t="b" s="14">
-        <v>1</v>
+      <c r="D24" t="s" s="13">
+        <v>38</v>
       </c>
       <c r="E24" s="15"/>
       <c r="F24" s="9"/>
@@ -3366,27 +3324,27 @@
       <c r="H24" t="s" s="13">
         <v>37</v>
       </c>
-      <c r="I24" t="b" s="14">
-        <v>1</v>
+      <c r="I24" t="s" s="13">
+        <v>39</v>
       </c>
     </row>
     <row r="25" ht="15.35" customHeight="1">
       <c r="A25" s="5"/>
       <c r="B25" s="16"/>
       <c r="C25" t="s" s="13">
-        <v>38</v>
-      </c>
-      <c r="D25" t="s" s="13">
-        <v>39</v>
-      </c>
-      <c r="E25" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="D25" s="18">
+        <v>44986</v>
+      </c>
+      <c r="E25" s="19"/>
       <c r="F25" s="9"/>
       <c r="G25" s="16"/>
       <c r="H25" t="s" s="13">
-        <v>38</v>
-      </c>
-      <c r="I25" t="s" s="13">
         <v>40</v>
+      </c>
+      <c r="I25" s="18">
+        <v>44621</v>
       </c>
     </row>
     <row r="26" ht="15.35" customHeight="1">
@@ -3395,798 +3353,786 @@
       <c r="C26" t="s" s="13">
         <v>41</v>
       </c>
-      <c r="D26" s="17">
-        <v>44986</v>
-      </c>
-      <c r="E26" s="18"/>
+      <c r="D26" t="s" s="13">
+        <v>42</v>
+      </c>
+      <c r="E26" s="15"/>
       <c r="F26" s="9"/>
       <c r="G26" s="16"/>
       <c r="H26" t="s" s="13">
         <v>41</v>
       </c>
-      <c r="I26" s="17">
-        <v>44621</v>
+      <c r="I26" t="s" s="13">
+        <v>43</v>
       </c>
     </row>
     <row r="27" ht="15.35" customHeight="1">
       <c r="A27" s="5"/>
       <c r="B27" s="16"/>
       <c r="C27" t="s" s="13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s" s="13">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E27" s="15"/>
       <c r="F27" s="9"/>
       <c r="G27" s="16"/>
       <c r="H27" t="s" s="13">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="I27" t="s" s="13">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" ht="15.35" customHeight="1">
       <c r="A28" s="5"/>
       <c r="B28" s="16"/>
       <c r="C28" t="s" s="13">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D28" t="s" s="13">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E28" s="15"/>
       <c r="F28" s="9"/>
       <c r="G28" s="16"/>
       <c r="H28" t="s" s="13">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I28" t="s" s="13">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" ht="15.35" customHeight="1">
       <c r="A29" s="5"/>
-      <c r="B29" s="16"/>
+      <c r="B29" s="20"/>
       <c r="C29" t="s" s="13">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D29" t="s" s="13">
+        <v>49</v>
+      </c>
+      <c r="E29" s="21"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="20"/>
+      <c r="H29" t="s" s="13">
         <v>48</v>
       </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="16"/>
-      <c r="H29" t="s" s="13">
-        <v>47</v>
-      </c>
       <c r="I29" t="s" s="13">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" ht="15.35" customHeight="1">
       <c r="A30" s="5"/>
-      <c r="B30" s="19"/>
-      <c r="C30" t="s" s="13">
-        <v>49</v>
-      </c>
-      <c r="D30" t="s" s="13">
+      <c r="B30" t="s" s="22">
         <v>50</v>
       </c>
-      <c r="E30" s="20"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="19"/>
-      <c r="H30" t="s" s="13">
-        <v>49</v>
-      </c>
-      <c r="I30" t="s" s="13">
+      <c r="C30" t="s" s="22">
+        <v>51</v>
+      </c>
+      <c r="D30" t="s" s="22">
+        <v>52</v>
+      </c>
+      <c r="E30" t="s" s="22">
+        <v>53</v>
+      </c>
+      <c r="F30" s="23"/>
+      <c r="G30" t="s" s="22">
         <v>50</v>
       </c>
+      <c r="H30" t="s" s="22">
+        <v>54</v>
+      </c>
+      <c r="I30" s="24"/>
     </row>
     <row r="31" ht="15.35" customHeight="1">
       <c r="A31" s="5"/>
-      <c r="B31" t="s" s="21">
-        <v>51</v>
-      </c>
-      <c r="C31" t="s" s="21">
-        <v>52</v>
-      </c>
-      <c r="D31" t="s" s="21">
-        <v>53</v>
-      </c>
-      <c r="E31" t="s" s="21">
-        <v>54</v>
-      </c>
-      <c r="F31" s="22"/>
-      <c r="G31" t="s" s="21">
-        <v>51</v>
-      </c>
-      <c r="H31" t="s" s="21">
+      <c r="B31" t="s" s="25">
         <v>55</v>
       </c>
-      <c r="I31" s="23"/>
+      <c r="C31" t="s" s="26">
+        <v>56</v>
+      </c>
+      <c r="D31" t="s" s="26">
+        <v>57</v>
+      </c>
+      <c r="E31" t="s" s="26">
+        <v>58</v>
+      </c>
+      <c r="F31" s="23"/>
+      <c r="G31" t="s" s="25">
+        <v>55</v>
+      </c>
+      <c r="H31" t="s" s="27">
+        <v>56</v>
+      </c>
+      <c r="I31" s="28"/>
     </row>
     <row r="32" ht="15.35" customHeight="1">
       <c r="A32" s="5"/>
-      <c r="B32" t="s" s="24">
-        <v>56</v>
-      </c>
-      <c r="C32" t="s" s="25">
-        <v>57</v>
-      </c>
-      <c r="D32" t="s" s="25">
-        <v>58</v>
-      </c>
-      <c r="E32" t="s" s="25">
+      <c r="B32" t="s" s="25">
         <v>59</v>
       </c>
-      <c r="F32" s="22"/>
-      <c r="G32" t="s" s="24">
-        <v>56</v>
-      </c>
-      <c r="H32" t="s" s="26">
-        <v>57</v>
-      </c>
-      <c r="I32" s="27"/>
+      <c r="C32" t="s" s="26">
+        <v>60</v>
+      </c>
+      <c r="D32" t="s" s="26">
+        <v>61</v>
+      </c>
+      <c r="E32" t="s" s="26">
+        <v>62</v>
+      </c>
+      <c r="F32" s="23"/>
+      <c r="G32" t="s" s="25">
+        <v>59</v>
+      </c>
+      <c r="H32" t="s" s="27">
+        <v>60</v>
+      </c>
+      <c r="I32" s="28"/>
     </row>
     <row r="33" ht="15.35" customHeight="1">
       <c r="A33" s="5"/>
-      <c r="B33" t="s" s="24">
-        <v>60</v>
-      </c>
-      <c r="C33" t="s" s="25">
-        <v>61</v>
-      </c>
-      <c r="D33" t="s" s="25">
-        <v>62</v>
-      </c>
-      <c r="E33" t="s" s="25">
+      <c r="B33" t="s" s="25">
         <v>63</v>
       </c>
-      <c r="F33" s="22"/>
-      <c r="G33" t="s" s="24">
-        <v>60</v>
-      </c>
-      <c r="H33" t="s" s="26">
-        <v>61</v>
-      </c>
-      <c r="I33" s="27"/>
+      <c r="C33" t="s" s="26">
+        <v>64</v>
+      </c>
+      <c r="D33" t="s" s="26">
+        <v>65</v>
+      </c>
+      <c r="E33" t="s" s="26">
+        <v>66</v>
+      </c>
+      <c r="F33" s="23"/>
+      <c r="G33" t="s" s="25">
+        <v>63</v>
+      </c>
+      <c r="H33" t="s" s="27">
+        <v>64</v>
+      </c>
+      <c r="I33" s="28"/>
     </row>
     <row r="34" ht="15.35" customHeight="1">
       <c r="A34" s="5"/>
-      <c r="B34" t="s" s="24">
-        <v>64</v>
-      </c>
-      <c r="C34" t="s" s="25">
-        <v>65</v>
-      </c>
-      <c r="D34" t="s" s="25">
-        <v>66</v>
-      </c>
-      <c r="E34" t="s" s="25">
+      <c r="B34" t="s" s="25">
         <v>67</v>
       </c>
-      <c r="F34" s="22"/>
-      <c r="G34" t="s" s="24">
-        <v>64</v>
-      </c>
-      <c r="H34" t="s" s="26">
-        <v>65</v>
-      </c>
-      <c r="I34" s="27"/>
+      <c r="C34" t="s" s="26">
+        <v>68</v>
+      </c>
+      <c r="D34" t="s" s="26">
+        <v>69</v>
+      </c>
+      <c r="E34" t="s" s="26">
+        <v>70</v>
+      </c>
+      <c r="F34" s="23"/>
+      <c r="G34" t="s" s="25">
+        <v>67</v>
+      </c>
+      <c r="H34" t="s" s="27">
+        <v>68</v>
+      </c>
+      <c r="I34" s="28"/>
     </row>
     <row r="35" ht="15.35" customHeight="1">
       <c r="A35" s="5"/>
-      <c r="B35" t="s" s="24">
-        <v>68</v>
-      </c>
-      <c r="C35" t="s" s="25">
-        <v>69</v>
-      </c>
-      <c r="D35" t="s" s="25">
-        <v>70</v>
-      </c>
-      <c r="E35" t="s" s="25">
+      <c r="B35" t="s" s="25">
         <v>71</v>
       </c>
-      <c r="F35" s="22"/>
-      <c r="G35" t="s" s="24">
-        <v>68</v>
-      </c>
-      <c r="H35" t="s" s="26">
-        <v>69</v>
-      </c>
-      <c r="I35" s="27"/>
+      <c r="C35" t="s" s="26">
+        <v>72</v>
+      </c>
+      <c r="D35" t="s" s="26">
+        <v>73</v>
+      </c>
+      <c r="E35" t="s" s="26">
+        <v>74</v>
+      </c>
+      <c r="F35" s="23"/>
+      <c r="G35" t="s" s="25">
+        <v>71</v>
+      </c>
+      <c r="H35" t="s" s="27">
+        <v>72</v>
+      </c>
+      <c r="I35" s="28"/>
     </row>
     <row r="36" ht="15.35" customHeight="1">
       <c r="A36" s="5"/>
-      <c r="B36" t="s" s="24">
-        <v>72</v>
-      </c>
-      <c r="C36" t="s" s="25">
-        <v>73</v>
-      </c>
-      <c r="D36" t="s" s="25">
-        <v>74</v>
-      </c>
-      <c r="E36" t="s" s="25">
+      <c r="B36" t="s" s="25">
         <v>75</v>
       </c>
-      <c r="F36" s="22"/>
-      <c r="G36" t="s" s="24">
-        <v>72</v>
-      </c>
-      <c r="H36" t="s" s="26">
-        <v>73</v>
-      </c>
-      <c r="I36" s="27"/>
+      <c r="C36" t="s" s="26">
+        <v>76</v>
+      </c>
+      <c r="D36" t="s" s="26">
+        <v>77</v>
+      </c>
+      <c r="E36" t="s" s="26">
+        <v>78</v>
+      </c>
+      <c r="F36" s="23"/>
+      <c r="G36" t="s" s="25">
+        <v>75</v>
+      </c>
+      <c r="H36" t="s" s="27">
+        <v>76</v>
+      </c>
+      <c r="I36" s="28"/>
     </row>
     <row r="37" ht="15.35" customHeight="1">
       <c r="A37" s="5"/>
-      <c r="B37" t="s" s="24">
-        <v>76</v>
-      </c>
-      <c r="C37" t="s" s="25">
-        <v>77</v>
-      </c>
-      <c r="D37" t="s" s="25">
-        <v>78</v>
-      </c>
-      <c r="E37" t="s" s="25">
+      <c r="B37" t="s" s="25">
         <v>79</v>
       </c>
-      <c r="F37" s="22"/>
-      <c r="G37" t="s" s="24">
-        <v>76</v>
-      </c>
-      <c r="H37" t="s" s="26">
-        <v>77</v>
-      </c>
-      <c r="I37" s="27"/>
+      <c r="C37" t="s" s="26">
+        <v>80</v>
+      </c>
+      <c r="D37" t="s" s="26">
+        <v>81</v>
+      </c>
+      <c r="E37" t="s" s="26">
+        <v>82</v>
+      </c>
+      <c r="F37" s="23"/>
+      <c r="G37" t="s" s="25">
+        <v>79</v>
+      </c>
+      <c r="H37" t="s" s="27">
+        <v>80</v>
+      </c>
+      <c r="I37" s="28"/>
     </row>
     <row r="38" ht="15.35" customHeight="1">
       <c r="A38" s="5"/>
-      <c r="B38" t="s" s="24">
-        <v>80</v>
-      </c>
-      <c r="C38" t="s" s="25">
-        <v>81</v>
-      </c>
-      <c r="D38" t="s" s="25">
-        <v>82</v>
-      </c>
-      <c r="E38" t="s" s="25">
+      <c r="B38" t="s" s="25">
         <v>83</v>
       </c>
-      <c r="F38" s="22"/>
-      <c r="G38" t="s" s="24">
-        <v>80</v>
-      </c>
-      <c r="H38" t="s" s="26">
-        <v>81</v>
-      </c>
-      <c r="I38" s="27"/>
+      <c r="C38" t="s" s="26">
+        <v>84</v>
+      </c>
+      <c r="D38" t="s" s="26">
+        <v>85</v>
+      </c>
+      <c r="E38" t="s" s="26">
+        <v>86</v>
+      </c>
+      <c r="F38" s="23"/>
+      <c r="G38" t="s" s="25">
+        <v>83</v>
+      </c>
+      <c r="H38" t="s" s="27">
+        <v>84</v>
+      </c>
+      <c r="I38" s="28"/>
     </row>
     <row r="39" ht="15.35" customHeight="1">
       <c r="A39" s="5"/>
-      <c r="B39" t="s" s="24">
-        <v>84</v>
-      </c>
-      <c r="C39" t="s" s="25">
-        <v>85</v>
-      </c>
-      <c r="D39" t="s" s="25">
-        <v>86</v>
-      </c>
-      <c r="E39" t="s" s="25">
+      <c r="B39" t="s" s="25">
         <v>87</v>
       </c>
-      <c r="F39" s="22"/>
-      <c r="G39" t="s" s="24">
-        <v>84</v>
-      </c>
-      <c r="H39" t="s" s="26">
-        <v>85</v>
-      </c>
-      <c r="I39" s="27"/>
+      <c r="C39" t="s" s="26">
+        <v>88</v>
+      </c>
+      <c r="D39" t="s" s="26">
+        <v>89</v>
+      </c>
+      <c r="E39" t="s" s="26">
+        <v>90</v>
+      </c>
+      <c r="F39" s="23"/>
+      <c r="G39" t="s" s="25">
+        <v>87</v>
+      </c>
+      <c r="H39" t="s" s="27">
+        <v>88</v>
+      </c>
+      <c r="I39" s="28"/>
     </row>
     <row r="40" ht="15.35" customHeight="1">
       <c r="A40" s="5"/>
-      <c r="B40" t="s" s="24">
-        <v>88</v>
-      </c>
-      <c r="C40" t="s" s="25">
-        <v>89</v>
-      </c>
-      <c r="D40" t="s" s="25">
-        <v>90</v>
-      </c>
-      <c r="E40" t="s" s="25">
+      <c r="B40" t="s" s="25">
         <v>91</v>
       </c>
-      <c r="F40" s="22"/>
-      <c r="G40" t="s" s="24">
-        <v>88</v>
-      </c>
-      <c r="H40" t="s" s="26">
-        <v>89</v>
-      </c>
-      <c r="I40" s="27"/>
+      <c r="C40" t="s" s="26">
+        <v>92</v>
+      </c>
+      <c r="D40" t="s" s="26">
+        <v>93</v>
+      </c>
+      <c r="E40" t="s" s="26">
+        <v>94</v>
+      </c>
+      <c r="F40" s="23"/>
+      <c r="G40" t="s" s="25">
+        <v>91</v>
+      </c>
+      <c r="H40" t="s" s="27">
+        <v>92</v>
+      </c>
+      <c r="I40" s="28"/>
     </row>
     <row r="41" ht="15.35" customHeight="1">
       <c r="A41" s="5"/>
-      <c r="B41" t="s" s="24">
-        <v>92</v>
-      </c>
-      <c r="C41" t="s" s="25">
-        <v>93</v>
-      </c>
-      <c r="D41" t="s" s="25">
-        <v>94</v>
-      </c>
-      <c r="E41" t="s" s="25">
+      <c r="B41" t="s" s="25">
         <v>95</v>
       </c>
-      <c r="F41" s="22"/>
-      <c r="G41" t="s" s="24">
-        <v>92</v>
-      </c>
-      <c r="H41" t="s" s="26">
-        <v>93</v>
-      </c>
-      <c r="I41" s="27"/>
+      <c r="C41" t="s" s="26">
+        <v>96</v>
+      </c>
+      <c r="D41" t="s" s="26">
+        <v>97</v>
+      </c>
+      <c r="E41" t="s" s="26">
+        <v>98</v>
+      </c>
+      <c r="F41" s="23"/>
+      <c r="G41" t="s" s="25">
+        <v>95</v>
+      </c>
+      <c r="H41" t="s" s="27">
+        <v>96</v>
+      </c>
+      <c r="I41" s="28"/>
     </row>
     <row r="42" ht="15.35" customHeight="1">
       <c r="A42" s="5"/>
-      <c r="B42" t="s" s="24">
-        <v>96</v>
-      </c>
-      <c r="C42" t="s" s="25">
-        <v>97</v>
-      </c>
-      <c r="D42" t="s" s="25">
-        <v>98</v>
-      </c>
-      <c r="E42" t="s" s="25">
+      <c r="B42" t="s" s="25">
         <v>99</v>
       </c>
-      <c r="F42" s="22"/>
-      <c r="G42" t="s" s="24">
-        <v>96</v>
-      </c>
-      <c r="H42" t="s" s="26">
-        <v>97</v>
-      </c>
-      <c r="I42" s="27"/>
+      <c r="C42" t="s" s="26">
+        <v>100</v>
+      </c>
+      <c r="D42" t="s" s="26">
+        <v>101</v>
+      </c>
+      <c r="E42" t="s" s="26">
+        <v>102</v>
+      </c>
+      <c r="F42" s="23"/>
+      <c r="G42" t="s" s="25">
+        <v>99</v>
+      </c>
+      <c r="H42" t="s" s="27">
+        <v>100</v>
+      </c>
+      <c r="I42" s="28"/>
     </row>
     <row r="43" ht="15.35" customHeight="1">
       <c r="A43" s="5"/>
-      <c r="B43" t="s" s="24">
-        <v>100</v>
-      </c>
-      <c r="C43" t="s" s="25">
-        <v>101</v>
-      </c>
-      <c r="D43" t="s" s="25">
-        <v>102</v>
-      </c>
-      <c r="E43" t="s" s="25">
+      <c r="B43" t="s" s="25">
         <v>103</v>
       </c>
-      <c r="F43" s="22"/>
-      <c r="G43" t="s" s="24">
-        <v>100</v>
-      </c>
-      <c r="H43" t="s" s="26">
-        <v>101</v>
-      </c>
-      <c r="I43" s="27"/>
+      <c r="C43" t="s" s="26">
+        <v>104</v>
+      </c>
+      <c r="D43" t="s" s="26">
+        <v>105</v>
+      </c>
+      <c r="E43" t="s" s="26">
+        <v>106</v>
+      </c>
+      <c r="F43" s="23"/>
+      <c r="G43" t="s" s="25">
+        <v>103</v>
+      </c>
+      <c r="H43" t="s" s="27">
+        <v>104</v>
+      </c>
+      <c r="I43" s="28"/>
     </row>
     <row r="44" ht="15.35" customHeight="1">
       <c r="A44" s="5"/>
-      <c r="B44" t="s" s="24">
-        <v>104</v>
-      </c>
-      <c r="C44" t="s" s="25">
-        <v>105</v>
-      </c>
-      <c r="D44" t="s" s="25">
-        <v>106</v>
-      </c>
-      <c r="E44" t="s" s="25">
+      <c r="B44" t="s" s="25">
         <v>107</v>
       </c>
-      <c r="F44" s="22"/>
-      <c r="G44" t="s" s="24">
-        <v>104</v>
-      </c>
-      <c r="H44" t="s" s="26">
-        <v>105</v>
-      </c>
-      <c r="I44" s="27"/>
+      <c r="C44" t="s" s="26">
+        <v>108</v>
+      </c>
+      <c r="D44" t="s" s="26">
+        <v>109</v>
+      </c>
+      <c r="E44" t="s" s="26">
+        <v>110</v>
+      </c>
+      <c r="F44" s="23"/>
+      <c r="G44" t="s" s="25">
+        <v>107</v>
+      </c>
+      <c r="H44" t="s" s="27">
+        <v>108</v>
+      </c>
+      <c r="I44" s="28"/>
     </row>
     <row r="45" ht="15.35" customHeight="1">
       <c r="A45" s="5"/>
-      <c r="B45" t="s" s="24">
-        <v>108</v>
-      </c>
-      <c r="C45" t="s" s="25">
-        <v>109</v>
-      </c>
-      <c r="D45" t="s" s="25">
-        <v>110</v>
-      </c>
-      <c r="E45" t="s" s="25">
+      <c r="B45" t="s" s="25">
         <v>111</v>
       </c>
-      <c r="F45" s="22"/>
-      <c r="G45" t="s" s="24">
-        <v>108</v>
-      </c>
-      <c r="H45" t="s" s="26">
-        <v>109</v>
-      </c>
-      <c r="I45" s="27"/>
+      <c r="C45" t="s" s="26">
+        <v>112</v>
+      </c>
+      <c r="D45" t="s" s="26">
+        <v>113</v>
+      </c>
+      <c r="E45" t="s" s="26">
+        <v>114</v>
+      </c>
+      <c r="F45" s="23"/>
+      <c r="G45" t="s" s="25">
+        <v>111</v>
+      </c>
+      <c r="H45" t="s" s="27">
+        <v>112</v>
+      </c>
+      <c r="I45" s="28"/>
     </row>
     <row r="46" ht="15.35" customHeight="1">
       <c r="A46" s="5"/>
-      <c r="B46" t="s" s="24">
-        <v>112</v>
-      </c>
-      <c r="C46" t="s" s="25">
-        <v>113</v>
-      </c>
-      <c r="D46" t="s" s="25">
-        <v>114</v>
-      </c>
-      <c r="E46" t="s" s="25">
+      <c r="B46" t="s" s="25">
         <v>115</v>
       </c>
-      <c r="F46" s="22"/>
-      <c r="G46" t="s" s="24">
-        <v>112</v>
-      </c>
-      <c r="H46" t="s" s="26">
-        <v>113</v>
-      </c>
-      <c r="I46" s="27"/>
+      <c r="C46" t="s" s="26">
+        <v>116</v>
+      </c>
+      <c r="D46" t="s" s="26">
+        <v>117</v>
+      </c>
+      <c r="E46" t="s" s="26">
+        <v>118</v>
+      </c>
+      <c r="F46" s="23"/>
+      <c r="G46" t="s" s="25">
+        <v>115</v>
+      </c>
+      <c r="H46" t="s" s="27">
+        <v>116</v>
+      </c>
+      <c r="I46" s="28"/>
     </row>
     <row r="47" ht="15.35" customHeight="1">
       <c r="A47" s="5"/>
-      <c r="B47" t="s" s="24">
-        <v>116</v>
-      </c>
-      <c r="C47" t="s" s="25">
-        <v>117</v>
-      </c>
-      <c r="D47" t="s" s="25">
-        <v>118</v>
-      </c>
-      <c r="E47" t="s" s="25">
+      <c r="B47" t="s" s="25">
         <v>119</v>
       </c>
-      <c r="F47" s="22"/>
-      <c r="G47" t="s" s="24">
-        <v>116</v>
-      </c>
-      <c r="H47" t="s" s="26">
-        <v>117</v>
-      </c>
-      <c r="I47" s="27"/>
+      <c r="C47" t="s" s="26">
+        <v>120</v>
+      </c>
+      <c r="D47" t="s" s="26">
+        <v>121</v>
+      </c>
+      <c r="E47" t="s" s="26">
+        <v>122</v>
+      </c>
+      <c r="F47" s="23"/>
+      <c r="G47" t="s" s="25">
+        <v>119</v>
+      </c>
+      <c r="H47" t="s" s="27">
+        <v>120</v>
+      </c>
+      <c r="I47" s="28"/>
     </row>
     <row r="48" ht="15.35" customHeight="1">
       <c r="A48" s="5"/>
-      <c r="B48" t="s" s="24">
-        <v>120</v>
-      </c>
-      <c r="C48" t="s" s="25">
-        <v>121</v>
-      </c>
-      <c r="D48" t="s" s="25">
-        <v>122</v>
-      </c>
-      <c r="E48" t="s" s="25">
+      <c r="B48" t="s" s="25">
         <v>123</v>
       </c>
-      <c r="F48" s="22"/>
-      <c r="G48" t="s" s="24">
-        <v>120</v>
-      </c>
-      <c r="H48" t="s" s="26">
-        <v>121</v>
-      </c>
-      <c r="I48" s="27"/>
+      <c r="C48" t="s" s="26">
+        <v>124</v>
+      </c>
+      <c r="D48" t="s" s="26">
+        <v>125</v>
+      </c>
+      <c r="E48" t="s" s="26">
+        <v>126</v>
+      </c>
+      <c r="F48" s="23"/>
+      <c r="G48" t="s" s="25">
+        <v>123</v>
+      </c>
+      <c r="H48" t="s" s="27">
+        <v>124</v>
+      </c>
+      <c r="I48" s="28"/>
     </row>
     <row r="49" ht="15.35" customHeight="1">
       <c r="A49" s="5"/>
-      <c r="B49" t="s" s="24">
-        <v>124</v>
-      </c>
-      <c r="C49" t="s" s="25">
-        <v>125</v>
-      </c>
-      <c r="D49" t="s" s="25">
-        <v>126</v>
-      </c>
-      <c r="E49" t="s" s="25">
+      <c r="B49" t="s" s="25">
         <v>127</v>
       </c>
-      <c r="F49" s="22"/>
-      <c r="G49" t="s" s="24">
-        <v>124</v>
-      </c>
-      <c r="H49" t="s" s="26">
-        <v>125</v>
-      </c>
-      <c r="I49" s="27"/>
+      <c r="C49" t="s" s="26">
+        <v>128</v>
+      </c>
+      <c r="D49" t="s" s="26">
+        <v>129</v>
+      </c>
+      <c r="E49" t="s" s="26">
+        <v>130</v>
+      </c>
+      <c r="F49" s="23"/>
+      <c r="G49" t="s" s="25">
+        <v>127</v>
+      </c>
+      <c r="H49" t="s" s="27">
+        <v>128</v>
+      </c>
+      <c r="I49" s="28"/>
     </row>
     <row r="50" ht="15.35" customHeight="1">
       <c r="A50" s="5"/>
-      <c r="B50" t="s" s="24">
-        <v>128</v>
-      </c>
-      <c r="C50" t="s" s="25">
-        <v>129</v>
-      </c>
-      <c r="D50" t="s" s="25">
-        <v>130</v>
-      </c>
-      <c r="E50" t="s" s="25">
+      <c r="B50" t="s" s="25">
         <v>131</v>
       </c>
-      <c r="F50" s="22"/>
-      <c r="G50" t="s" s="24">
-        <v>128</v>
-      </c>
-      <c r="H50" t="s" s="26">
-        <v>129</v>
-      </c>
-      <c r="I50" s="27"/>
+      <c r="C50" t="s" s="26">
+        <v>132</v>
+      </c>
+      <c r="D50" t="s" s="26">
+        <v>133</v>
+      </c>
+      <c r="E50" t="s" s="26">
+        <v>134</v>
+      </c>
+      <c r="F50" s="23"/>
+      <c r="G50" t="s" s="25">
+        <v>131</v>
+      </c>
+      <c r="H50" t="s" s="27">
+        <v>132</v>
+      </c>
+      <c r="I50" s="28"/>
     </row>
     <row r="51" ht="15.35" customHeight="1">
       <c r="A51" s="5"/>
-      <c r="B51" t="s" s="24">
-        <v>132</v>
-      </c>
-      <c r="C51" t="s" s="25">
-        <v>133</v>
-      </c>
-      <c r="D51" t="s" s="25">
-        <v>134</v>
-      </c>
-      <c r="E51" t="s" s="25">
+      <c r="B51" t="s" s="25">
         <v>135</v>
       </c>
-      <c r="F51" s="22"/>
-      <c r="G51" t="s" s="24">
-        <v>132</v>
-      </c>
-      <c r="H51" t="s" s="26">
-        <v>133</v>
-      </c>
-      <c r="I51" s="27"/>
+      <c r="C51" t="s" s="26">
+        <v>136</v>
+      </c>
+      <c r="D51" t="s" s="26">
+        <v>137</v>
+      </c>
+      <c r="E51" t="s" s="26">
+        <v>138</v>
+      </c>
+      <c r="F51" s="23"/>
+      <c r="G51" t="s" s="25">
+        <v>135</v>
+      </c>
+      <c r="H51" t="s" s="27">
+        <v>136</v>
+      </c>
+      <c r="I51" s="28"/>
     </row>
     <row r="52" ht="15.35" customHeight="1">
       <c r="A52" s="5"/>
-      <c r="B52" t="s" s="24">
-        <v>136</v>
-      </c>
-      <c r="C52" t="s" s="25">
-        <v>137</v>
-      </c>
-      <c r="D52" t="s" s="25">
-        <v>138</v>
-      </c>
-      <c r="E52" t="s" s="25">
+      <c r="B52" t="s" s="25">
         <v>139</v>
       </c>
-      <c r="F52" s="22"/>
-      <c r="G52" t="s" s="24">
-        <v>136</v>
-      </c>
-      <c r="H52" t="s" s="26">
-        <v>137</v>
-      </c>
-      <c r="I52" s="27"/>
+      <c r="C52" t="s" s="26">
+        <v>140</v>
+      </c>
+      <c r="D52" t="s" s="26">
+        <v>141</v>
+      </c>
+      <c r="E52" t="s" s="26">
+        <v>142</v>
+      </c>
+      <c r="F52" s="23"/>
+      <c r="G52" t="s" s="25">
+        <v>139</v>
+      </c>
+      <c r="H52" t="s" s="27">
+        <v>140</v>
+      </c>
+      <c r="I52" s="28"/>
     </row>
     <row r="53" ht="15.35" customHeight="1">
       <c r="A53" s="5"/>
-      <c r="B53" t="s" s="24">
-        <v>140</v>
-      </c>
-      <c r="C53" t="s" s="25">
-        <v>141</v>
-      </c>
-      <c r="D53" t="s" s="25">
-        <v>142</v>
-      </c>
-      <c r="E53" t="s" s="25">
+      <c r="B53" t="s" s="25">
         <v>143</v>
       </c>
-      <c r="F53" s="22"/>
-      <c r="G53" t="s" s="24">
-        <v>140</v>
-      </c>
-      <c r="H53" t="s" s="26">
-        <v>141</v>
-      </c>
-      <c r="I53" s="27"/>
+      <c r="C53" t="s" s="26">
+        <v>144</v>
+      </c>
+      <c r="D53" t="s" s="26">
+        <v>145</v>
+      </c>
+      <c r="E53" t="s" s="26">
+        <v>146</v>
+      </c>
+      <c r="F53" s="23"/>
+      <c r="G53" t="s" s="25">
+        <v>143</v>
+      </c>
+      <c r="H53" t="s" s="27">
+        <v>144</v>
+      </c>
+      <c r="I53" s="28"/>
     </row>
     <row r="54" ht="15.35" customHeight="1">
       <c r="A54" s="5"/>
-      <c r="B54" t="s" s="24">
-        <v>144</v>
-      </c>
-      <c r="C54" t="s" s="25">
-        <v>145</v>
-      </c>
-      <c r="D54" t="s" s="25">
-        <v>146</v>
-      </c>
-      <c r="E54" t="s" s="25">
+      <c r="B54" t="s" s="25">
         <v>147</v>
       </c>
-      <c r="F54" s="22"/>
-      <c r="G54" t="s" s="24">
-        <v>144</v>
-      </c>
-      <c r="H54" t="s" s="26">
-        <v>145</v>
-      </c>
-      <c r="I54" s="27"/>
+      <c r="C54" t="s" s="26">
+        <v>148</v>
+      </c>
+      <c r="D54" t="s" s="26">
+        <v>149</v>
+      </c>
+      <c r="E54" t="s" s="26">
+        <v>150</v>
+      </c>
+      <c r="F54" s="23"/>
+      <c r="G54" t="s" s="25">
+        <v>147</v>
+      </c>
+      <c r="H54" t="s" s="27">
+        <v>148</v>
+      </c>
+      <c r="I54" s="28"/>
     </row>
     <row r="55" ht="15.35" customHeight="1">
       <c r="A55" s="5"/>
-      <c r="B55" t="s" s="24">
-        <v>148</v>
-      </c>
-      <c r="C55" t="s" s="25">
-        <v>149</v>
-      </c>
-      <c r="D55" t="s" s="25">
-        <v>150</v>
-      </c>
-      <c r="E55" t="s" s="25">
+      <c r="B55" t="s" s="25">
         <v>151</v>
       </c>
-      <c r="F55" s="22"/>
-      <c r="G55" t="s" s="24">
-        <v>148</v>
-      </c>
-      <c r="H55" t="s" s="26">
-        <v>149</v>
-      </c>
-      <c r="I55" s="27"/>
+      <c r="C55" t="s" s="26">
+        <v>152</v>
+      </c>
+      <c r="D55" t="s" s="26">
+        <v>153</v>
+      </c>
+      <c r="E55" t="s" s="26">
+        <v>154</v>
+      </c>
+      <c r="F55" s="23"/>
+      <c r="G55" t="s" s="25">
+        <v>151</v>
+      </c>
+      <c r="H55" t="s" s="27">
+        <v>152</v>
+      </c>
+      <c r="I55" s="28"/>
     </row>
     <row r="56" ht="15.35" customHeight="1">
       <c r="A56" s="5"/>
-      <c r="B56" t="s" s="24">
-        <v>152</v>
-      </c>
-      <c r="C56" t="s" s="25">
-        <v>153</v>
-      </c>
-      <c r="D56" t="s" s="25">
-        <v>154</v>
-      </c>
-      <c r="E56" t="s" s="25">
+      <c r="B56" t="s" s="25">
         <v>155</v>
       </c>
-      <c r="F56" s="22"/>
-      <c r="G56" t="s" s="24">
-        <v>152</v>
-      </c>
-      <c r="H56" t="s" s="26">
-        <v>153</v>
-      </c>
-      <c r="I56" s="27"/>
+      <c r="C56" t="s" s="26">
+        <v>156</v>
+      </c>
+      <c r="D56" t="s" s="26">
+        <v>157</v>
+      </c>
+      <c r="E56" t="s" s="26">
+        <v>158</v>
+      </c>
+      <c r="F56" s="23"/>
+      <c r="G56" t="s" s="25">
+        <v>155</v>
+      </c>
+      <c r="H56" t="s" s="27">
+        <v>156</v>
+      </c>
+      <c r="I56" s="28"/>
     </row>
     <row r="57" ht="15.35" customHeight="1">
       <c r="A57" s="5"/>
-      <c r="B57" t="s" s="24">
-        <v>156</v>
-      </c>
-      <c r="C57" t="s" s="25">
-        <v>157</v>
-      </c>
-      <c r="D57" t="s" s="25">
-        <v>158</v>
-      </c>
-      <c r="E57" t="s" s="25">
+      <c r="B57" t="s" s="26">
         <v>159</v>
       </c>
-      <c r="F57" s="22"/>
-      <c r="G57" t="s" s="24">
-        <v>156</v>
-      </c>
-      <c r="H57" t="s" s="26">
-        <v>157</v>
-      </c>
-      <c r="I57" s="27"/>
+      <c r="C57" t="s" s="26">
+        <v>160</v>
+      </c>
+      <c r="D57" t="s" s="26">
+        <v>161</v>
+      </c>
+      <c r="E57" t="s" s="26">
+        <v>162</v>
+      </c>
+      <c r="F57" s="23"/>
+      <c r="G57" t="s" s="26">
+        <v>163</v>
+      </c>
+      <c r="H57" t="s" s="27">
+        <v>164</v>
+      </c>
+      <c r="I57" s="28"/>
     </row>
     <row r="58" ht="15.35" customHeight="1">
       <c r="A58" s="5"/>
-      <c r="B58" t="s" s="24">
-        <v>160</v>
-      </c>
-      <c r="C58" t="s" s="25">
-        <v>161</v>
-      </c>
-      <c r="D58" t="s" s="25">
-        <v>162</v>
-      </c>
-      <c r="E58" t="s" s="25">
-        <v>163</v>
-      </c>
-      <c r="F58" s="22"/>
-      <c r="G58" t="s" s="24">
-        <v>160</v>
-      </c>
-      <c r="H58" t="s" s="26">
-        <v>161</v>
-      </c>
-      <c r="I58" s="27"/>
+      <c r="B58" t="s" s="29">
+        <v>165</v>
+      </c>
+      <c r="C58" t="s" s="30">
+        <v>166</v>
+      </c>
+      <c r="D58" s="31"/>
+      <c r="E58" s="32"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
     </row>
     <row r="59" ht="15.35" customHeight="1">
       <c r="A59" s="5"/>
-      <c r="B59" t="s" s="25">
-        <v>164</v>
-      </c>
-      <c r="C59" t="s" s="25">
-        <v>165</v>
-      </c>
-      <c r="D59" t="s" s="25">
-        <v>166</v>
-      </c>
-      <c r="E59" t="s" s="25">
+      <c r="B59" t="s" s="33">
         <v>167</v>
       </c>
-      <c r="F59" s="22"/>
-      <c r="G59" t="s" s="25">
+      <c r="C59" t="s" s="34">
         <v>168</v>
       </c>
-      <c r="H59" t="s" s="26">
-        <v>169</v>
-      </c>
-      <c r="I59" s="27"/>
+      <c r="D59" s="35"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
     </row>
     <row r="60" ht="15.35" customHeight="1">
-      <c r="A60" s="5"/>
-      <c r="B60" t="s" s="28">
-        <v>170</v>
-      </c>
-      <c r="C60" t="s" s="29">
-        <v>171</v>
-      </c>
-      <c r="D60" s="30"/>
-      <c r="E60" s="31"/>
+      <c r="A60" s="2"/>
+      <c r="B60" s="36"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="2"/>
       <c r="F60" s="2"/>
-      <c r="G60" s="31"/>
-      <c r="H60" s="31"/>
-      <c r="I60" s="31"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
     </row>
     <row r="61" ht="15.35" customHeight="1">
       <c r="A61" s="5"/>
-      <c r="B61" t="s" s="32">
-        <v>172</v>
-      </c>
-      <c r="C61" t="s" s="33">
-        <v>173</v>
-      </c>
-      <c r="D61" s="34"/>
-      <c r="E61" s="2"/>
+      <c r="B61" t="s" s="10">
+        <v>169</v>
+      </c>
+      <c r="C61" s="11"/>
+      <c r="D61" s="11"/>
+      <c r="E61" s="35"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
     </row>
     <row r="62" ht="15.35" customHeight="1">
-      <c r="A62" s="2"/>
-      <c r="B62" s="35"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="2"/>
+      <c r="A62" s="5"/>
+      <c r="B62" t="s" s="26">
+        <v>170</v>
+      </c>
+      <c r="C62" t="s" s="26">
+        <v>91</v>
+      </c>
+      <c r="D62" t="s" s="26">
+        <v>171</v>
+      </c>
+      <c r="E62" s="35"/>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
@@ -4194,12 +4140,16 @@
     </row>
     <row r="63" ht="15.35" customHeight="1">
       <c r="A63" s="5"/>
-      <c r="B63" t="s" s="10">
-        <v>174</v>
-      </c>
-      <c r="C63" s="11"/>
-      <c r="D63" s="11"/>
-      <c r="E63" s="34"/>
+      <c r="B63" t="s" s="26">
+        <v>172</v>
+      </c>
+      <c r="C63" t="s" s="26">
+        <v>172</v>
+      </c>
+      <c r="D63" t="s" s="26">
+        <v>173</v>
+      </c>
+      <c r="E63" s="35"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
@@ -4207,16 +4157,16 @@
     </row>
     <row r="64" ht="15.35" customHeight="1">
       <c r="A64" s="5"/>
-      <c r="B64" t="s" s="25">
+      <c r="B64" t="s" s="37">
+        <v>174</v>
+      </c>
+      <c r="C64" t="s" s="37">
         <v>175</v>
       </c>
-      <c r="C64" t="s" s="25">
-        <v>96</v>
-      </c>
-      <c r="D64" t="s" s="25">
-        <v>176</v>
-      </c>
-      <c r="E64" s="34"/>
+      <c r="D64" t="b" s="38">
+        <v>0</v>
+      </c>
+      <c r="E64" s="35"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
@@ -4224,16 +4174,16 @@
     </row>
     <row r="65" ht="15.35" customHeight="1">
       <c r="A65" s="5"/>
-      <c r="B65" t="s" s="25">
+      <c r="B65" t="s" s="37">
+        <v>176</v>
+      </c>
+      <c r="C65" t="s" s="37">
         <v>177</v>
       </c>
-      <c r="C65" t="s" s="25">
-        <v>177</v>
-      </c>
-      <c r="D65" t="s" s="25">
-        <v>178</v>
-      </c>
-      <c r="E65" s="34"/>
+      <c r="D65" t="b" s="38">
+        <v>1</v>
+      </c>
+      <c r="E65" s="35"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
@@ -4241,16 +4191,16 @@
     </row>
     <row r="66" ht="15.35" customHeight="1">
       <c r="A66" s="5"/>
-      <c r="B66" t="s" s="36">
+      <c r="B66" t="s" s="37">
+        <v>178</v>
+      </c>
+      <c r="C66" t="s" s="37">
         <v>179</v>
       </c>
-      <c r="C66" t="s" s="36">
-        <v>180</v>
-      </c>
-      <c r="D66" t="b" s="37">
-        <v>0</v>
-      </c>
-      <c r="E66" s="34"/>
+      <c r="D66" t="b" s="38">
+        <v>1</v>
+      </c>
+      <c r="E66" s="35"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
@@ -4258,16 +4208,16 @@
     </row>
     <row r="67" ht="15.35" customHeight="1">
       <c r="A67" s="5"/>
-      <c r="B67" t="s" s="36">
+      <c r="B67" t="s" s="37">
+        <v>180</v>
+      </c>
+      <c r="C67" t="s" s="37">
         <v>181</v>
       </c>
-      <c r="C67" t="s" s="36">
-        <v>182</v>
-      </c>
-      <c r="D67" t="b" s="37">
-        <v>1</v>
-      </c>
-      <c r="E67" s="34"/>
+      <c r="D67" t="s" s="26">
+        <v>6</v>
+      </c>
+      <c r="E67" s="35"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
@@ -4275,16 +4225,16 @@
     </row>
     <row r="68" ht="15.35" customHeight="1">
       <c r="A68" s="5"/>
-      <c r="B68" t="s" s="36">
+      <c r="B68" t="s" s="37">
+        <v>182</v>
+      </c>
+      <c r="C68" t="s" s="37">
         <v>183</v>
       </c>
-      <c r="C68" t="s" s="36">
+      <c r="D68" t="s" s="26">
         <v>184</v>
       </c>
-      <c r="D68" t="b" s="37">
-        <v>1</v>
-      </c>
-      <c r="E68" s="34"/>
+      <c r="E68" s="35"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
@@ -4292,16 +4242,16 @@
     </row>
     <row r="69" ht="15.35" customHeight="1">
       <c r="A69" s="5"/>
-      <c r="B69" t="s" s="36">
+      <c r="B69" t="s" s="37">
         <v>185</v>
       </c>
-      <c r="C69" t="s" s="36">
+      <c r="C69" t="s" s="37">
         <v>186</v>
       </c>
-      <c r="D69" t="s" s="25">
-        <v>6</v>
-      </c>
-      <c r="E69" s="34"/>
+      <c r="D69" t="s" s="26">
+        <v>187</v>
+      </c>
+      <c r="E69" s="35"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
@@ -4309,16 +4259,16 @@
     </row>
     <row r="70" ht="15.35" customHeight="1">
       <c r="A70" s="5"/>
-      <c r="B70" t="s" s="36">
-        <v>187</v>
-      </c>
-      <c r="C70" t="s" s="36">
+      <c r="B70" t="s" s="37">
         <v>188</v>
       </c>
-      <c r="D70" t="s" s="25">
+      <c r="C70" t="s" s="37">
         <v>189</v>
       </c>
-      <c r="E70" s="34"/>
+      <c r="D70" t="s" s="26">
+        <v>13</v>
+      </c>
+      <c r="E70" s="35"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
@@ -4326,16 +4276,16 @@
     </row>
     <row r="71" ht="15.35" customHeight="1">
       <c r="A71" s="5"/>
-      <c r="B71" t="s" s="36">
+      <c r="B71" t="s" s="37">
         <v>190</v>
       </c>
-      <c r="C71" t="s" s="36">
+      <c r="C71" t="s" s="37">
         <v>191</v>
       </c>
-      <c r="D71" t="s" s="25">
+      <c r="D71" t="s" s="26">
         <v>192</v>
       </c>
-      <c r="E71" s="34"/>
+      <c r="E71" s="35"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
@@ -4343,16 +4293,16 @@
     </row>
     <row r="72" ht="15.35" customHeight="1">
       <c r="A72" s="5"/>
-      <c r="B72" t="s" s="36">
+      <c r="B72" t="s" s="37">
         <v>193</v>
       </c>
-      <c r="C72" t="s" s="36">
+      <c r="C72" t="s" s="37">
         <v>194</v>
       </c>
-      <c r="D72" t="b" s="37">
-        <v>1</v>
-      </c>
-      <c r="E72" s="34"/>
+      <c r="D72" t="s" s="26">
+        <v>195</v>
+      </c>
+      <c r="E72" s="35"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
@@ -4360,16 +4310,16 @@
     </row>
     <row r="73" ht="15.35" customHeight="1">
       <c r="A73" s="5"/>
-      <c r="B73" t="s" s="36">
-        <v>195</v>
-      </c>
-      <c r="C73" t="s" s="36">
+      <c r="B73" t="s" s="37">
         <v>196</v>
       </c>
-      <c r="D73" t="s" s="25">
-        <v>14</v>
-      </c>
-      <c r="E73" s="34"/>
+      <c r="C73" t="s" s="37">
+        <v>197</v>
+      </c>
+      <c r="D73" t="s" s="26">
+        <v>20</v>
+      </c>
+      <c r="E73" s="35"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
@@ -4377,16 +4327,16 @@
     </row>
     <row r="74" ht="15.35" customHeight="1">
       <c r="A74" s="5"/>
-      <c r="B74" t="s" s="36">
-        <v>197</v>
-      </c>
-      <c r="C74" t="s" s="36">
+      <c r="B74" t="s" s="37">
         <v>198</v>
       </c>
-      <c r="D74" t="s" s="25">
+      <c r="C74" t="s" s="37">
         <v>199</v>
       </c>
-      <c r="E74" s="34"/>
+      <c r="D74" s="39">
+        <v>45002</v>
+      </c>
+      <c r="E74" s="40"/>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
@@ -4394,16 +4344,16 @@
     </row>
     <row r="75" ht="15.35" customHeight="1">
       <c r="A75" s="5"/>
-      <c r="B75" t="s" s="36">
+      <c r="B75" t="s" s="37">
         <v>200</v>
       </c>
-      <c r="C75" t="s" s="36">
+      <c r="C75" t="s" s="37">
         <v>201</v>
       </c>
-      <c r="D75" t="s" s="25">
-        <v>202</v>
-      </c>
-      <c r="E75" s="34"/>
+      <c r="D75" s="39">
+        <v>45172</v>
+      </c>
+      <c r="E75" s="40"/>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
@@ -4411,16 +4361,16 @@
     </row>
     <row r="76" ht="15.35" customHeight="1">
       <c r="A76" s="5"/>
-      <c r="B76" t="s" s="36">
+      <c r="B76" t="s" s="37">
+        <v>202</v>
+      </c>
+      <c r="C76" t="s" s="37">
         <v>203</v>
       </c>
-      <c r="C76" t="s" s="36">
-        <v>204</v>
-      </c>
-      <c r="D76" t="s" s="25">
-        <v>21</v>
-      </c>
-      <c r="E76" s="34"/>
+      <c r="D76" s="39">
+        <v>44993</v>
+      </c>
+      <c r="E76" s="40"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
@@ -4428,16 +4378,16 @@
     </row>
     <row r="77" ht="15.35" customHeight="1">
       <c r="A77" s="5"/>
-      <c r="B77" t="s" s="36">
+      <c r="B77" t="s" s="37">
+        <v>204</v>
+      </c>
+      <c r="C77" t="s" s="37">
         <v>205</v>
       </c>
-      <c r="C77" t="s" s="36">
-        <v>206</v>
-      </c>
-      <c r="D77" s="38">
-        <v>45002</v>
-      </c>
-      <c r="E77" s="39"/>
+      <c r="D77" t="s" s="26">
+        <v>26</v>
+      </c>
+      <c r="E77" s="35"/>
       <c r="F77" s="2"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
@@ -4445,16 +4395,16 @@
     </row>
     <row r="78" ht="15.35" customHeight="1">
       <c r="A78" s="5"/>
-      <c r="B78" t="s" s="36">
+      <c r="B78" t="s" s="37">
+        <v>206</v>
+      </c>
+      <c r="C78" t="s" s="37">
         <v>207</v>
       </c>
-      <c r="C78" t="s" s="36">
+      <c r="D78" t="s" s="26">
         <v>208</v>
       </c>
-      <c r="D78" s="38">
-        <v>45172</v>
-      </c>
-      <c r="E78" s="39"/>
+      <c r="E78" s="35"/>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
@@ -4462,16 +4412,16 @@
     </row>
     <row r="79" ht="15.35" customHeight="1">
       <c r="A79" s="5"/>
-      <c r="B79" t="s" s="36">
+      <c r="B79" t="s" s="37">
         <v>209</v>
       </c>
-      <c r="C79" t="s" s="36">
+      <c r="C79" t="s" s="37">
         <v>210</v>
       </c>
-      <c r="D79" s="38">
-        <v>44993</v>
-      </c>
-      <c r="E79" s="39"/>
+      <c r="D79" t="s" s="26">
+        <v>211</v>
+      </c>
+      <c r="E79" s="35"/>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
@@ -4479,16 +4429,16 @@
     </row>
     <row r="80" ht="15.35" customHeight="1">
       <c r="A80" s="5"/>
-      <c r="B80" t="s" s="36">
-        <v>211</v>
-      </c>
-      <c r="C80" t="s" s="36">
+      <c r="B80" t="s" s="37">
         <v>212</v>
       </c>
-      <c r="D80" t="s" s="25">
-        <v>27</v>
-      </c>
-      <c r="E80" s="34"/>
+      <c r="C80" t="s" s="37">
+        <v>213</v>
+      </c>
+      <c r="D80" t="s" s="26">
+        <v>33</v>
+      </c>
+      <c r="E80" s="35"/>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
@@ -4496,16 +4446,16 @@
     </row>
     <row r="81" ht="15.35" customHeight="1">
       <c r="A81" s="5"/>
-      <c r="B81" t="s" s="36">
-        <v>213</v>
-      </c>
-      <c r="C81" t="s" s="36">
+      <c r="B81" t="s" s="37">
         <v>214</v>
       </c>
-      <c r="D81" t="s" s="25">
+      <c r="C81" t="s" s="37">
         <v>215</v>
       </c>
-      <c r="E81" s="34"/>
+      <c r="D81" t="s" s="26">
+        <v>35</v>
+      </c>
+      <c r="E81" s="35"/>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
@@ -4513,16 +4463,16 @@
     </row>
     <row r="82" ht="15.35" customHeight="1">
       <c r="A82" s="5"/>
-      <c r="B82" t="s" s="36">
+      <c r="B82" t="s" s="37">
         <v>216</v>
       </c>
-      <c r="C82" t="s" s="36">
+      <c r="C82" t="s" s="37">
         <v>217</v>
       </c>
-      <c r="D82" t="s" s="25">
-        <v>218</v>
-      </c>
-      <c r="E82" s="34"/>
+      <c r="D82" t="b" s="38">
+        <v>1</v>
+      </c>
+      <c r="E82" s="35"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
@@ -4530,16 +4480,16 @@
     </row>
     <row r="83" ht="15.35" customHeight="1">
       <c r="A83" s="5"/>
-      <c r="B83" t="s" s="36">
+      <c r="B83" t="s" s="37">
+        <v>218</v>
+      </c>
+      <c r="C83" t="s" s="37">
         <v>219</v>
       </c>
-      <c r="C83" t="s" s="36">
-        <v>220</v>
-      </c>
-      <c r="D83" t="s" s="25">
-        <v>34</v>
-      </c>
-      <c r="E83" s="34"/>
+      <c r="D83" t="s" s="26">
+        <v>38</v>
+      </c>
+      <c r="E83" s="35"/>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
@@ -4547,16 +4497,16 @@
     </row>
     <row r="84" ht="15.35" customHeight="1">
       <c r="A84" s="5"/>
-      <c r="B84" t="s" s="36">
+      <c r="B84" t="s" s="37">
+        <v>220</v>
+      </c>
+      <c r="C84" t="s" s="37">
         <v>221</v>
       </c>
-      <c r="C84" t="s" s="36">
-        <v>222</v>
-      </c>
-      <c r="D84" t="s" s="25">
-        <v>36</v>
-      </c>
-      <c r="E84" s="34"/>
+      <c r="D84" s="39">
+        <v>44986</v>
+      </c>
+      <c r="E84" s="40"/>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
@@ -4564,16 +4514,16 @@
     </row>
     <row r="85" ht="15.35" customHeight="1">
       <c r="A85" s="5"/>
-      <c r="B85" t="s" s="36">
+      <c r="B85" t="s" s="37">
+        <v>222</v>
+      </c>
+      <c r="C85" t="s" s="37">
         <v>223</v>
       </c>
-      <c r="C85" t="s" s="36">
+      <c r="D85" t="s" s="26">
         <v>224</v>
       </c>
-      <c r="D85" t="b" s="37">
-        <v>1</v>
-      </c>
-      <c r="E85" s="34"/>
+      <c r="E85" s="35"/>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
@@ -4581,16 +4531,16 @@
     </row>
     <row r="86" ht="15.35" customHeight="1">
       <c r="A86" s="5"/>
-      <c r="B86" t="s" s="36">
+      <c r="B86" t="s" s="37">
         <v>225</v>
       </c>
-      <c r="C86" t="s" s="36">
+      <c r="C86" t="s" s="37">
         <v>226</v>
       </c>
-      <c r="D86" t="s" s="25">
-        <v>39</v>
-      </c>
-      <c r="E86" s="34"/>
+      <c r="D86" t="s" s="26">
+        <v>227</v>
+      </c>
+      <c r="E86" s="35"/>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
@@ -4598,16 +4548,16 @@
     </row>
     <row r="87" ht="15.35" customHeight="1">
       <c r="A87" s="5"/>
-      <c r="B87" t="s" s="36">
-        <v>227</v>
-      </c>
-      <c r="C87" t="s" s="36">
+      <c r="B87" t="s" s="37">
         <v>228</v>
       </c>
-      <c r="D87" s="38">
-        <v>44986</v>
-      </c>
-      <c r="E87" s="39"/>
+      <c r="C87" t="s" s="37">
+        <v>229</v>
+      </c>
+      <c r="D87" t="s" s="26">
+        <v>230</v>
+      </c>
+      <c r="E87" s="35"/>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
@@ -4615,16 +4565,16 @@
     </row>
     <row r="88" ht="15.35" customHeight="1">
       <c r="A88" s="5"/>
-      <c r="B88" t="s" s="36">
-        <v>229</v>
-      </c>
-      <c r="C88" t="s" s="36">
-        <v>230</v>
-      </c>
-      <c r="D88" t="s" s="25">
+      <c r="B88" t="s" s="37">
         <v>231</v>
       </c>
-      <c r="E88" s="34"/>
+      <c r="C88" t="s" s="37">
+        <v>232</v>
+      </c>
+      <c r="D88" t="s" s="26">
+        <v>49</v>
+      </c>
+      <c r="E88" s="35"/>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
@@ -4632,16 +4582,16 @@
     </row>
     <row r="89" ht="15.35" customHeight="1">
       <c r="A89" s="5"/>
-      <c r="B89" t="s" s="36">
-        <v>232</v>
-      </c>
-      <c r="C89" t="s" s="36">
+      <c r="B89" t="s" s="37">
         <v>233</v>
       </c>
-      <c r="D89" t="s" s="25">
+      <c r="C89" t="s" s="37">
         <v>234</v>
       </c>
-      <c r="E89" s="34"/>
+      <c r="D89" t="b" s="38">
+        <v>1</v>
+      </c>
+      <c r="E89" s="35"/>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
@@ -4649,16 +4599,16 @@
     </row>
     <row r="90" ht="15.35" customHeight="1">
       <c r="A90" s="5"/>
-      <c r="B90" t="s" s="36">
+      <c r="B90" t="s" s="41">
         <v>235</v>
       </c>
-      <c r="C90" t="s" s="36">
+      <c r="C90" t="s" s="41">
         <v>236</v>
       </c>
-      <c r="D90" t="s" s="25">
-        <v>237</v>
-      </c>
-      <c r="E90" s="34"/>
+      <c r="D90" t="b" s="38">
+        <v>0</v>
+      </c>
+      <c r="E90" s="35"/>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
@@ -4666,16 +4616,16 @@
     </row>
     <row r="91" ht="15.35" customHeight="1">
       <c r="A91" s="5"/>
-      <c r="B91" t="s" s="36">
+      <c r="B91" t="s" s="41">
+        <v>237</v>
+      </c>
+      <c r="C91" t="s" s="41">
         <v>238</v>
       </c>
-      <c r="C91" t="s" s="36">
-        <v>239</v>
-      </c>
-      <c r="D91" t="s" s="25">
-        <v>50</v>
-      </c>
-      <c r="E91" s="34"/>
+      <c r="D91" t="b" s="38">
+        <v>1</v>
+      </c>
+      <c r="E91" s="35"/>
       <c r="F91" s="2"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
@@ -4683,16 +4633,16 @@
     </row>
     <row r="92" ht="15.35" customHeight="1">
       <c r="A92" s="5"/>
-      <c r="B92" t="s" s="36">
+      <c r="B92" t="s" s="41">
+        <v>239</v>
+      </c>
+      <c r="C92" t="s" s="41">
         <v>240</v>
       </c>
-      <c r="C92" t="s" s="36">
-        <v>241</v>
-      </c>
-      <c r="D92" t="b" s="37">
+      <c r="D92" t="b" s="38">
         <v>1</v>
       </c>
-      <c r="E92" s="34"/>
+      <c r="E92" s="35"/>
       <c r="F92" s="2"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
@@ -4700,16 +4650,16 @@
     </row>
     <row r="93" ht="15.35" customHeight="1">
       <c r="A93" s="5"/>
-      <c r="B93" t="s" s="40">
+      <c r="B93" t="s" s="41">
+        <v>241</v>
+      </c>
+      <c r="C93" t="s" s="41">
         <v>242</v>
       </c>
-      <c r="C93" t="s" s="40">
-        <v>243</v>
-      </c>
-      <c r="D93" t="b" s="37">
-        <v>0</v>
-      </c>
-      <c r="E93" s="34"/>
+      <c r="D93" t="s" s="26">
+        <v>7</v>
+      </c>
+      <c r="E93" s="35"/>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
@@ -4717,16 +4667,16 @@
     </row>
     <row r="94" ht="15.35" customHeight="1">
       <c r="A94" s="5"/>
-      <c r="B94" t="s" s="40">
+      <c r="B94" t="s" s="41">
+        <v>243</v>
+      </c>
+      <c r="C94" t="s" s="41">
         <v>244</v>
       </c>
-      <c r="C94" t="s" s="40">
-        <v>245</v>
-      </c>
-      <c r="D94" t="b" s="37">
-        <v>1</v>
-      </c>
-      <c r="E94" s="34"/>
+      <c r="D94" t="s" s="26">
+        <v>184</v>
+      </c>
+      <c r="E94" s="35"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
@@ -4734,16 +4684,16 @@
     </row>
     <row r="95" ht="15.35" customHeight="1">
       <c r="A95" s="5"/>
-      <c r="B95" t="s" s="40">
+      <c r="B95" t="s" s="41">
+        <v>245</v>
+      </c>
+      <c r="C95" t="s" s="41">
         <v>246</v>
       </c>
-      <c r="C95" t="s" s="40">
-        <v>247</v>
-      </c>
-      <c r="D95" t="b" s="37">
-        <v>1</v>
-      </c>
-      <c r="E95" s="34"/>
+      <c r="D95" t="s" s="26">
+        <v>187</v>
+      </c>
+      <c r="E95" s="35"/>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
@@ -4751,16 +4701,16 @@
     </row>
     <row r="96" ht="15.35" customHeight="1">
       <c r="A96" s="5"/>
-      <c r="B96" t="s" s="40">
+      <c r="B96" t="s" s="41">
+        <v>247</v>
+      </c>
+      <c r="C96" t="s" s="41">
         <v>248</v>
       </c>
-      <c r="C96" t="s" s="40">
-        <v>249</v>
-      </c>
-      <c r="D96" t="s" s="25">
-        <v>7</v>
-      </c>
-      <c r="E96" s="34"/>
+      <c r="D96" t="s" s="26">
+        <v>14</v>
+      </c>
+      <c r="E96" s="35"/>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
@@ -4768,16 +4718,16 @@
     </row>
     <row r="97" ht="15.35" customHeight="1">
       <c r="A97" s="5"/>
-      <c r="B97" t="s" s="40">
+      <c r="B97" t="s" s="41">
+        <v>249</v>
+      </c>
+      <c r="C97" t="s" s="41">
         <v>250</v>
       </c>
-      <c r="C97" t="s" s="40">
-        <v>251</v>
-      </c>
-      <c r="D97" t="s" s="25">
-        <v>189</v>
-      </c>
-      <c r="E97" s="34"/>
+      <c r="D97" t="s" s="26">
+        <v>192</v>
+      </c>
+      <c r="E97" s="35"/>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
@@ -4785,16 +4735,16 @@
     </row>
     <row r="98" ht="15.35" customHeight="1">
       <c r="A98" s="5"/>
-      <c r="B98" t="s" s="40">
+      <c r="B98" t="s" s="41">
+        <v>251</v>
+      </c>
+      <c r="C98" t="s" s="41">
         <v>252</v>
       </c>
-      <c r="C98" t="s" s="40">
-        <v>253</v>
-      </c>
-      <c r="D98" t="s" s="25">
-        <v>192</v>
-      </c>
-      <c r="E98" s="34"/>
+      <c r="D98" t="s" s="26">
+        <v>195</v>
+      </c>
+      <c r="E98" s="35"/>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
@@ -4802,16 +4752,16 @@
     </row>
     <row r="99" ht="15.35" customHeight="1">
       <c r="A99" s="5"/>
-      <c r="B99" t="s" s="40">
+      <c r="B99" t="s" s="41">
+        <v>253</v>
+      </c>
+      <c r="C99" t="s" s="41">
         <v>254</v>
       </c>
-      <c r="C99" t="s" s="40">
-        <v>255</v>
-      </c>
-      <c r="D99" t="b" s="37">
-        <v>1</v>
-      </c>
-      <c r="E99" s="34"/>
+      <c r="D99" t="s" s="26">
+        <v>21</v>
+      </c>
+      <c r="E99" s="35"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
@@ -4819,16 +4769,16 @@
     </row>
     <row r="100" ht="15.35" customHeight="1">
       <c r="A100" s="5"/>
-      <c r="B100" t="s" s="40">
+      <c r="B100" t="s" s="41">
+        <v>255</v>
+      </c>
+      <c r="C100" t="s" s="41">
         <v>256</v>
       </c>
-      <c r="C100" t="s" s="40">
-        <v>257</v>
-      </c>
-      <c r="D100" t="s" s="25">
-        <v>15</v>
-      </c>
-      <c r="E100" s="34"/>
+      <c r="D100" s="39">
+        <v>44621</v>
+      </c>
+      <c r="E100" s="40"/>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
@@ -4836,16 +4786,16 @@
     </row>
     <row r="101" ht="15.35" customHeight="1">
       <c r="A101" s="5"/>
-      <c r="B101" t="s" s="40">
+      <c r="B101" t="s" s="41">
+        <v>257</v>
+      </c>
+      <c r="C101" t="s" s="41">
         <v>258</v>
       </c>
-      <c r="C101" t="s" s="40">
-        <v>259</v>
-      </c>
-      <c r="D101" t="s" s="25">
-        <v>199</v>
-      </c>
-      <c r="E101" s="34"/>
+      <c r="D101" s="39">
+        <v>44629</v>
+      </c>
+      <c r="E101" s="40"/>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
@@ -4853,16 +4803,16 @@
     </row>
     <row r="102" ht="15.35" customHeight="1">
       <c r="A102" s="5"/>
-      <c r="B102" t="s" s="40">
+      <c r="B102" t="s" s="41">
+        <v>259</v>
+      </c>
+      <c r="C102" t="s" s="41">
         <v>260</v>
       </c>
-      <c r="C102" t="s" s="40">
-        <v>261</v>
-      </c>
-      <c r="D102" t="s" s="25">
-        <v>202</v>
-      </c>
-      <c r="E102" s="34"/>
+      <c r="D102" s="39">
+        <v>44628</v>
+      </c>
+      <c r="E102" s="40"/>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
@@ -4870,16 +4820,16 @@
     </row>
     <row r="103" ht="15.35" customHeight="1">
       <c r="A103" s="5"/>
-      <c r="B103" t="s" s="40">
+      <c r="B103" t="s" s="41">
+        <v>261</v>
+      </c>
+      <c r="C103" t="s" s="41">
         <v>262</v>
       </c>
-      <c r="C103" t="s" s="40">
-        <v>263</v>
-      </c>
-      <c r="D103" t="s" s="25">
-        <v>22</v>
-      </c>
-      <c r="E103" s="34"/>
+      <c r="D103" t="s" s="26">
+        <v>27</v>
+      </c>
+      <c r="E103" s="35"/>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
@@ -4887,16 +4837,16 @@
     </row>
     <row r="104" ht="15.35" customHeight="1">
       <c r="A104" s="5"/>
-      <c r="B104" t="s" s="40">
+      <c r="B104" t="s" s="41">
+        <v>263</v>
+      </c>
+      <c r="C104" t="s" s="41">
         <v>264</v>
       </c>
-      <c r="C104" t="s" s="40">
-        <v>265</v>
-      </c>
-      <c r="D104" s="38">
-        <v>44621</v>
-      </c>
-      <c r="E104" s="39"/>
+      <c r="D104" t="s" s="26">
+        <v>208</v>
+      </c>
+      <c r="E104" s="35"/>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
@@ -4904,16 +4854,16 @@
     </row>
     <row r="105" ht="15.35" customHeight="1">
       <c r="A105" s="5"/>
-      <c r="B105" t="s" s="40">
+      <c r="B105" t="s" s="41">
+        <v>265</v>
+      </c>
+      <c r="C105" t="s" s="41">
         <v>266</v>
       </c>
-      <c r="C105" t="s" s="40">
-        <v>267</v>
-      </c>
-      <c r="D105" s="38">
-        <v>44629</v>
-      </c>
-      <c r="E105" s="39"/>
+      <c r="D105" t="s" s="26">
+        <v>211</v>
+      </c>
+      <c r="E105" s="35"/>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
@@ -4921,16 +4871,16 @@
     </row>
     <row r="106" ht="15.35" customHeight="1">
       <c r="A106" s="5"/>
-      <c r="B106" t="s" s="40">
+      <c r="B106" t="s" s="41">
+        <v>267</v>
+      </c>
+      <c r="C106" t="s" s="41">
         <v>268</v>
       </c>
-      <c r="C106" t="s" s="40">
-        <v>269</v>
-      </c>
-      <c r="D106" s="38">
-        <v>44628</v>
-      </c>
-      <c r="E106" s="39"/>
+      <c r="D106" t="s" s="26">
+        <v>33</v>
+      </c>
+      <c r="E106" s="35"/>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
@@ -4938,16 +4888,16 @@
     </row>
     <row r="107" ht="15.35" customHeight="1">
       <c r="A107" s="5"/>
-      <c r="B107" t="s" s="40">
+      <c r="B107" t="s" s="41">
+        <v>269</v>
+      </c>
+      <c r="C107" t="s" s="41">
         <v>270</v>
       </c>
-      <c r="C107" t="s" s="40">
-        <v>271</v>
-      </c>
-      <c r="D107" t="s" s="25">
-        <v>28</v>
-      </c>
-      <c r="E107" s="34"/>
+      <c r="D107" t="s" s="26">
+        <v>35</v>
+      </c>
+      <c r="E107" s="35"/>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
@@ -4955,16 +4905,16 @@
     </row>
     <row r="108" ht="15.35" customHeight="1">
       <c r="A108" s="5"/>
-      <c r="B108" t="s" s="40">
+      <c r="B108" t="s" s="41">
+        <v>271</v>
+      </c>
+      <c r="C108" t="s" s="41">
         <v>272</v>
       </c>
-      <c r="C108" t="s" s="40">
-        <v>273</v>
-      </c>
-      <c r="D108" t="s" s="25">
-        <v>215</v>
-      </c>
-      <c r="E108" s="34"/>
+      <c r="D108" t="b" s="38">
+        <v>1</v>
+      </c>
+      <c r="E108" s="35"/>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
@@ -4972,16 +4922,16 @@
     </row>
     <row r="109" ht="15.35" customHeight="1">
       <c r="A109" s="5"/>
-      <c r="B109" t="s" s="40">
+      <c r="B109" t="s" s="41">
+        <v>273</v>
+      </c>
+      <c r="C109" t="s" s="41">
         <v>274</v>
       </c>
-      <c r="C109" t="s" s="40">
-        <v>275</v>
-      </c>
-      <c r="D109" t="s" s="25">
-        <v>218</v>
-      </c>
-      <c r="E109" s="34"/>
+      <c r="D109" t="s" s="26">
+        <v>39</v>
+      </c>
+      <c r="E109" s="35"/>
       <c r="F109" s="2"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
@@ -4989,16 +4939,16 @@
     </row>
     <row r="110" ht="15.35" customHeight="1">
       <c r="A110" s="5"/>
-      <c r="B110" t="s" s="40">
+      <c r="B110" t="s" s="41">
+        <v>275</v>
+      </c>
+      <c r="C110" t="s" s="41">
         <v>276</v>
       </c>
-      <c r="C110" t="s" s="40">
-        <v>277</v>
-      </c>
-      <c r="D110" t="s" s="25">
-        <v>34</v>
-      </c>
-      <c r="E110" s="34"/>
+      <c r="D110" s="39">
+        <v>44621</v>
+      </c>
+      <c r="E110" s="40"/>
       <c r="F110" s="2"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
@@ -5006,16 +4956,16 @@
     </row>
     <row r="111" ht="15.35" customHeight="1">
       <c r="A111" s="5"/>
-      <c r="B111" t="s" s="40">
+      <c r="B111" t="s" s="41">
+        <v>277</v>
+      </c>
+      <c r="C111" t="s" s="41">
         <v>278</v>
       </c>
-      <c r="C111" t="s" s="40">
+      <c r="D111" t="s" s="26">
         <v>279</v>
       </c>
-      <c r="D111" t="s" s="25">
-        <v>36</v>
-      </c>
-      <c r="E111" s="34"/>
+      <c r="E111" s="35"/>
       <c r="F111" s="2"/>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
@@ -5023,16 +4973,16 @@
     </row>
     <row r="112" ht="15.35" customHeight="1">
       <c r="A112" s="5"/>
-      <c r="B112" t="s" s="40">
+      <c r="B112" t="s" s="41">
         <v>280</v>
       </c>
-      <c r="C112" t="s" s="40">
+      <c r="C112" t="s" s="41">
         <v>281</v>
       </c>
-      <c r="D112" t="b" s="37">
-        <v>1</v>
-      </c>
-      <c r="E112" s="34"/>
+      <c r="D112" t="s" s="26">
+        <v>227</v>
+      </c>
+      <c r="E112" s="35"/>
       <c r="F112" s="2"/>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
@@ -5040,16 +4990,16 @@
     </row>
     <row r="113" ht="15.35" customHeight="1">
       <c r="A113" s="5"/>
-      <c r="B113" t="s" s="40">
+      <c r="B113" t="s" s="41">
         <v>282</v>
       </c>
-      <c r="C113" t="s" s="40">
+      <c r="C113" t="s" s="41">
         <v>283</v>
       </c>
-      <c r="D113" t="s" s="25">
-        <v>40</v>
-      </c>
-      <c r="E113" s="34"/>
+      <c r="D113" t="s" s="26">
+        <v>230</v>
+      </c>
+      <c r="E113" s="35"/>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
@@ -5057,16 +5007,16 @@
     </row>
     <row r="114" ht="15.35" customHeight="1">
       <c r="A114" s="5"/>
-      <c r="B114" t="s" s="40">
+      <c r="B114" t="s" s="41">
         <v>284</v>
       </c>
-      <c r="C114" t="s" s="40">
+      <c r="C114" t="s" s="41">
         <v>285</v>
       </c>
-      <c r="D114" s="38">
-        <v>44621</v>
-      </c>
-      <c r="E114" s="39"/>
+      <c r="D114" t="s" s="26">
+        <v>49</v>
+      </c>
+      <c r="E114" s="35"/>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
@@ -5074,16 +5024,16 @@
     </row>
     <row r="115" ht="15.35" customHeight="1">
       <c r="A115" s="5"/>
-      <c r="B115" t="s" s="40">
+      <c r="B115" t="s" s="41">
         <v>286</v>
       </c>
-      <c r="C115" t="s" s="40">
+      <c r="C115" t="s" s="41">
         <v>287</v>
       </c>
-      <c r="D115" t="s" s="25">
-        <v>288</v>
-      </c>
-      <c r="E115" s="34"/>
+      <c r="D115" t="b" s="38">
+        <v>1</v>
+      </c>
+      <c r="E115" s="35"/>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
@@ -5091,16 +5041,16 @@
     </row>
     <row r="116" ht="15.35" customHeight="1">
       <c r="A116" s="5"/>
-      <c r="B116" t="s" s="40">
+      <c r="B116" t="s" s="42">
+        <v>288</v>
+      </c>
+      <c r="C116" t="s" s="42">
+        <v>283</v>
+      </c>
+      <c r="D116" t="s" s="43">
         <v>289</v>
       </c>
-      <c r="C116" t="s" s="40">
-        <v>290</v>
-      </c>
-      <c r="D116" t="s" s="25">
-        <v>234</v>
-      </c>
-      <c r="E116" s="34"/>
+      <c r="E116" s="2"/>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
@@ -5108,16 +5058,16 @@
     </row>
     <row r="117" ht="15.35" customHeight="1">
       <c r="A117" s="5"/>
-      <c r="B117" t="s" s="40">
+      <c r="B117" t="s" s="42">
+        <v>290</v>
+      </c>
+      <c r="C117" t="s" s="42">
+        <v>285</v>
+      </c>
+      <c r="D117" t="s" s="26">
         <v>291</v>
       </c>
-      <c r="C117" t="s" s="40">
-        <v>292</v>
-      </c>
-      <c r="D117" t="s" s="25">
-        <v>237</v>
-      </c>
-      <c r="E117" s="34"/>
+      <c r="E117" s="35"/>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
@@ -5125,49 +5075,37 @@
     </row>
     <row r="118" ht="15.35" customHeight="1">
       <c r="A118" s="5"/>
-      <c r="B118" t="s" s="40">
+      <c r="B118" t="s" s="42">
+        <v>292</v>
+      </c>
+      <c r="C118" t="s" s="42">
+        <v>287</v>
+      </c>
+      <c r="D118" t="s" s="26">
         <v>293</v>
       </c>
-      <c r="C118" t="s" s="40">
-        <v>294</v>
-      </c>
-      <c r="D118" t="s" s="25">
-        <v>50</v>
-      </c>
-      <c r="E118" s="34"/>
+      <c r="E118" s="35"/>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
     </row>
     <row r="119" ht="15.35" customHeight="1">
-      <c r="A119" s="5"/>
-      <c r="B119" t="s" s="40">
-        <v>295</v>
-      </c>
-      <c r="C119" t="s" s="40">
-        <v>296</v>
-      </c>
-      <c r="D119" t="b" s="37">
-        <v>1</v>
-      </c>
-      <c r="E119" s="34"/>
+      <c r="A119" s="2"/>
+      <c r="B119" s="32"/>
+      <c r="C119" s="32"/>
+      <c r="D119" s="32"/>
+      <c r="E119" s="2"/>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
     </row>
     <row r="120" ht="15.35" customHeight="1">
-      <c r="A120" s="5"/>
-      <c r="B120" t="s" s="41">
-        <v>297</v>
-      </c>
-      <c r="C120" t="s" s="41">
-        <v>292</v>
-      </c>
-      <c r="D120" t="s" s="42">
-        <v>298</v>
-      </c>
+      <c r="A120" s="2"/>
+      <c r="B120" s="2"/>
+      <c r="C120" s="2"/>
+      <c r="D120" s="2"/>
       <c r="E120" s="2"/>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
@@ -5175,441 +5113,447 @@
       <c r="I120" s="2"/>
     </row>
     <row r="121" ht="15.35" customHeight="1">
-      <c r="A121" s="5"/>
-      <c r="B121" t="s" s="41">
-        <v>299</v>
-      </c>
-      <c r="C121" t="s" s="41">
-        <v>294</v>
-      </c>
-      <c r="D121" t="s" s="25">
-        <v>300</v>
-      </c>
-      <c r="E121" s="34"/>
+      <c r="A121" s="2"/>
+      <c r="B121" s="2"/>
+      <c r="C121" s="2"/>
+      <c r="D121" s="2"/>
+      <c r="E121" s="2"/>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
     </row>
     <row r="122" ht="15.35" customHeight="1">
-      <c r="A122" s="5"/>
-      <c r="B122" t="s" s="41">
-        <v>301</v>
-      </c>
-      <c r="C122" t="s" s="41">
-        <v>296</v>
-      </c>
-      <c r="D122" t="s" s="25">
-        <v>302</v>
-      </c>
-      <c r="E122" s="34"/>
+      <c r="A122" s="2"/>
+      <c r="B122" s="4"/>
+      <c r="C122" s="2"/>
+      <c r="D122" s="2"/>
+      <c r="E122" s="2"/>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
       <c r="I122" s="2"/>
     </row>
     <row r="123" ht="15.35" customHeight="1">
-      <c r="A123" s="2"/>
-      <c r="B123" s="31"/>
-      <c r="C123" s="31"/>
-      <c r="D123" s="31"/>
+      <c r="A123" s="5"/>
+      <c r="B123" t="s" s="10">
+        <v>294</v>
+      </c>
+      <c r="C123" s="44"/>
+      <c r="D123" s="4"/>
       <c r="E123" s="2"/>
-      <c r="F123" s="2"/>
+      <c r="F123" s="4"/>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
     </row>
     <row r="124" ht="15.35" customHeight="1">
-      <c r="A124" s="2"/>
-      <c r="B124" s="2"/>
-      <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
-      <c r="E124" s="2"/>
-      <c r="F124" s="2"/>
-      <c r="G124" s="2"/>
-      <c r="H124" s="2"/>
+      <c r="A124" s="5"/>
+      <c r="B124" t="s" s="13">
+        <v>1</v>
+      </c>
+      <c r="C124" t="s" s="13">
+        <v>41</v>
+      </c>
+      <c r="D124" t="s" s="13">
+        <v>42</v>
+      </c>
+      <c r="E124" s="23"/>
+      <c r="F124" t="s" s="10">
+        <v>294</v>
+      </c>
+      <c r="G124" s="44"/>
+      <c r="H124" s="4"/>
       <c r="I124" s="2"/>
     </row>
     <row r="125" ht="15.35" customHeight="1">
-      <c r="A125" s="2"/>
-      <c r="B125" s="2"/>
-      <c r="C125" s="2"/>
-      <c r="D125" s="2"/>
-      <c r="E125" s="2"/>
-      <c r="F125" s="2"/>
-      <c r="G125" s="2"/>
-      <c r="H125" s="2"/>
-      <c r="I125" s="2"/>
+      <c r="A125" s="5"/>
+      <c r="B125" s="45"/>
+      <c r="C125" t="s" s="13">
+        <v>22</v>
+      </c>
+      <c r="D125" s="18">
+        <v>45209</v>
+      </c>
+      <c r="E125" s="23"/>
+      <c r="F125" t="s" s="46">
+        <v>1</v>
+      </c>
+      <c r="G125" t="s" s="13">
+        <v>22</v>
+      </c>
+      <c r="H125" s="18">
+        <v>45240</v>
+      </c>
+      <c r="I125" s="35"/>
     </row>
     <row r="126" ht="15.35" customHeight="1">
-      <c r="A126" s="2"/>
-      <c r="B126" s="4"/>
-      <c r="C126" s="2"/>
-      <c r="D126" s="2"/>
-      <c r="E126" s="2"/>
-      <c r="F126" s="2"/>
-      <c r="G126" s="2"/>
-      <c r="H126" s="2"/>
-      <c r="I126" s="2"/>
+      <c r="A126" s="5"/>
+      <c r="B126" s="45"/>
+      <c r="C126" t="s" s="13">
+        <v>295</v>
+      </c>
+      <c r="D126" t="b" s="14">
+        <v>1</v>
+      </c>
+      <c r="E126" s="23"/>
+      <c r="F126" s="47"/>
+      <c r="G126" t="s" s="13">
+        <v>295</v>
+      </c>
+      <c r="H126" t="b" s="14">
+        <v>0</v>
+      </c>
+      <c r="I126" s="35"/>
     </row>
     <row r="127" ht="15.35" customHeight="1">
       <c r="A127" s="5"/>
-      <c r="B127" t="s" s="10">
-        <v>303</v>
-      </c>
-      <c r="C127" s="43"/>
-      <c r="D127" s="4"/>
-      <c r="E127" s="2"/>
-      <c r="F127" s="4"/>
-      <c r="G127" s="2"/>
-      <c r="H127" s="2"/>
-      <c r="I127" s="2"/>
+      <c r="B127" s="24"/>
+      <c r="C127" t="s" s="13">
+        <v>296</v>
+      </c>
+      <c r="D127" t="s" s="13">
+        <v>297</v>
+      </c>
+      <c r="E127" s="23"/>
+      <c r="F127" s="24"/>
+      <c r="G127" t="s" s="13">
+        <v>296</v>
+      </c>
+      <c r="H127" t="s" s="13">
+        <v>298</v>
+      </c>
+      <c r="I127" s="35"/>
     </row>
     <row r="128" ht="15.35" customHeight="1">
       <c r="A128" s="5"/>
-      <c r="B128" t="s" s="13">
+      <c r="B128" s="45"/>
+      <c r="C128" t="s" s="13">
+        <v>36</v>
+      </c>
+      <c r="D128" t="b" s="14">
         <v>1</v>
       </c>
-      <c r="C128" t="s" s="13">
-        <v>42</v>
-      </c>
-      <c r="D128" t="s" s="13">
-        <v>43</v>
-      </c>
-      <c r="E128" s="22"/>
-      <c r="F128" t="s" s="10">
-        <v>303</v>
-      </c>
-      <c r="G128" s="43"/>
-      <c r="H128" s="4"/>
-      <c r="I128" s="2"/>
+      <c r="E128" s="23"/>
+      <c r="F128" s="47"/>
+      <c r="G128" t="s" s="13">
+        <v>36</v>
+      </c>
+      <c r="H128" t="b" s="14">
+        <v>0</v>
+      </c>
+      <c r="I128" s="35"/>
     </row>
     <row r="129" ht="15.35" customHeight="1">
       <c r="A129" s="5"/>
-      <c r="B129" s="44"/>
+      <c r="B129" s="45"/>
       <c r="C129" t="s" s="13">
-        <v>23</v>
-      </c>
-      <c r="D129" s="17">
-        <v>45209</v>
-      </c>
-      <c r="E129" s="22"/>
-      <c r="F129" t="s" s="45">
-        <v>1</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="D129" t="s" s="13">
+        <v>300</v>
+      </c>
+      <c r="E129" s="23"/>
+      <c r="F129" s="47"/>
       <c r="G129" t="s" s="13">
-        <v>23</v>
-      </c>
-      <c r="H129" s="17">
-        <v>45240</v>
-      </c>
-      <c r="I129" s="34"/>
+        <v>299</v>
+      </c>
+      <c r="H129" t="s" s="13">
+        <v>300</v>
+      </c>
+      <c r="I129" s="35"/>
     </row>
     <row r="130" ht="15.35" customHeight="1">
       <c r="A130" s="5"/>
-      <c r="B130" s="44"/>
+      <c r="B130" s="45"/>
       <c r="C130" t="s" s="13">
-        <v>304</v>
-      </c>
-      <c r="D130" t="b" s="14">
-        <v>1</v>
-      </c>
-      <c r="E130" s="22"/>
-      <c r="F130" s="46"/>
+        <v>5</v>
+      </c>
+      <c r="D130" t="s" s="13">
+        <v>6</v>
+      </c>
+      <c r="E130" s="23"/>
+      <c r="F130" s="47"/>
       <c r="G130" t="s" s="13">
-        <v>304</v>
-      </c>
-      <c r="H130" t="b" s="14">
-        <v>0</v>
-      </c>
-      <c r="I130" s="34"/>
+        <v>5</v>
+      </c>
+      <c r="H130" t="s" s="13">
+        <v>7</v>
+      </c>
+      <c r="I130" s="35"/>
     </row>
     <row r="131" ht="15.35" customHeight="1">
       <c r="A131" s="5"/>
-      <c r="B131" s="44"/>
+      <c r="B131" s="45"/>
       <c r="C131" t="s" s="13">
-        <v>12</v>
-      </c>
-      <c r="D131" t="b" s="14">
-        <v>1</v>
-      </c>
-      <c r="E131" s="22"/>
-      <c r="F131" s="46"/>
+        <v>25</v>
+      </c>
+      <c r="D131" t="s" s="13">
+        <v>301</v>
+      </c>
+      <c r="E131" s="23"/>
+      <c r="F131" s="47"/>
       <c r="G131" t="s" s="13">
-        <v>12</v>
-      </c>
-      <c r="H131" t="b" s="14">
-        <v>0</v>
-      </c>
-      <c r="I131" s="34"/>
+        <v>25</v>
+      </c>
+      <c r="H131" t="s" s="13">
+        <v>302</v>
+      </c>
+      <c r="I131" s="35"/>
     </row>
     <row r="132" ht="15.35" customHeight="1">
       <c r="A132" s="5"/>
-      <c r="B132" s="23"/>
-      <c r="C132" t="s" s="13">
+      <c r="B132" t="s" s="26">
+        <v>303</v>
+      </c>
+      <c r="C132" t="s" s="26">
+        <v>304</v>
+      </c>
+      <c r="D132" s="24"/>
+      <c r="E132" s="23"/>
+      <c r="F132" t="s" s="13">
+        <v>303</v>
+      </c>
+      <c r="G132" t="s" s="13">
+        <v>304</v>
+      </c>
+      <c r="H132" s="45"/>
+      <c r="I132" s="35"/>
+    </row>
+    <row r="133" ht="165.35" customHeight="1">
+      <c r="A133" s="5"/>
+      <c r="B133" t="s" s="26">
         <v>305</v>
       </c>
-      <c r="D132" t="s" s="13">
+      <c r="C133" t="s" s="48">
         <v>306</v>
       </c>
-      <c r="E132" s="22"/>
-      <c r="F132" s="23"/>
-      <c r="G132" t="s" s="13">
+      <c r="D133" s="49"/>
+      <c r="E133" s="23"/>
+      <c r="F133" t="s" s="26">
         <v>305</v>
       </c>
-      <c r="H132" t="s" s="13">
-        <v>307</v>
-      </c>
-      <c r="I132" s="34"/>
-    </row>
-    <row r="133" ht="15.35" customHeight="1">
-      <c r="A133" s="5"/>
-      <c r="B133" s="44"/>
-      <c r="C133" t="s" s="13">
-        <v>37</v>
-      </c>
-      <c r="D133" t="b" s="14">
-        <v>1</v>
-      </c>
-      <c r="E133" s="22"/>
-      <c r="F133" s="46"/>
-      <c r="G133" t="s" s="13">
-        <v>37</v>
-      </c>
-      <c r="H133" t="b" s="14">
-        <v>0</v>
-      </c>
-      <c r="I133" s="34"/>
+      <c r="G133" t="s" s="48">
+        <v>306</v>
+      </c>
+      <c r="H133" s="49"/>
+      <c r="I133" s="35"/>
     </row>
     <row r="134" ht="15.35" customHeight="1">
       <c r="A134" s="5"/>
-      <c r="B134" s="44"/>
-      <c r="C134" t="s" s="13">
+      <c r="B134" t="s" s="26">
+        <v>307</v>
+      </c>
+      <c r="C134" t="s" s="26">
         <v>308</v>
       </c>
-      <c r="D134" t="s" s="13">
-        <v>309</v>
-      </c>
-      <c r="E134" s="22"/>
-      <c r="F134" s="46"/>
-      <c r="G134" t="s" s="13">
+      <c r="D134" s="24"/>
+      <c r="E134" s="23"/>
+      <c r="F134" t="s" s="26">
+        <v>307</v>
+      </c>
+      <c r="G134" t="s" s="26">
         <v>308</v>
       </c>
-      <c r="H134" t="s" s="13">
-        <v>309</v>
-      </c>
-      <c r="I134" s="34"/>
+      <c r="H134" s="24"/>
+      <c r="I134" s="35"/>
     </row>
     <row r="135" ht="15.35" customHeight="1">
       <c r="A135" s="5"/>
-      <c r="B135" s="44"/>
-      <c r="C135" t="s" s="13">
-        <v>5</v>
-      </c>
-      <c r="D135" t="s" s="13">
-        <v>6</v>
-      </c>
-      <c r="E135" s="22"/>
-      <c r="F135" s="46"/>
-      <c r="G135" t="s" s="13">
-        <v>5</v>
-      </c>
-      <c r="H135" t="s" s="13">
-        <v>7</v>
-      </c>
-      <c r="I135" s="34"/>
+      <c r="B135" t="s" s="26">
+        <v>309</v>
+      </c>
+      <c r="C135" t="s" s="26">
+        <v>310</v>
+      </c>
+      <c r="D135" s="24"/>
+      <c r="E135" s="23"/>
+      <c r="F135" t="s" s="26">
+        <v>309</v>
+      </c>
+      <c r="G135" t="s" s="26">
+        <v>310</v>
+      </c>
+      <c r="H135" s="24"/>
+      <c r="I135" s="35"/>
     </row>
     <row r="136" ht="15.35" customHeight="1">
       <c r="A136" s="5"/>
-      <c r="B136" s="44"/>
-      <c r="C136" t="s" s="13">
-        <v>26</v>
-      </c>
-      <c r="D136" t="s" s="13">
-        <v>310</v>
-      </c>
-      <c r="E136" s="22"/>
-      <c r="F136" s="46"/>
-      <c r="G136" t="s" s="13">
-        <v>26</v>
-      </c>
-      <c r="H136" t="s" s="13">
-        <v>311</v>
-      </c>
-      <c r="I136" s="34"/>
+      <c r="B136" s="38">
+        <v>1</v>
+      </c>
+      <c r="C136" s="38">
+        <v>100</v>
+      </c>
+      <c r="D136" s="24"/>
+      <c r="E136" s="23"/>
+      <c r="F136" s="38">
+        <v>1</v>
+      </c>
+      <c r="G136" s="50">
+        <v>100</v>
+      </c>
+      <c r="H136" s="51"/>
+      <c r="I136" s="35"/>
     </row>
     <row r="137" ht="15.35" customHeight="1">
       <c r="A137" s="5"/>
-      <c r="B137" t="s" s="25">
-        <v>312</v>
-      </c>
-      <c r="C137" t="s" s="25">
-        <v>313</v>
-      </c>
-      <c r="D137" s="23"/>
-      <c r="E137" s="22"/>
-      <c r="F137" t="s" s="13">
-        <v>312</v>
-      </c>
-      <c r="G137" t="s" s="13">
-        <v>313</v>
-      </c>
-      <c r="H137" s="44"/>
-      <c r="I137" s="34"/>
-    </row>
-    <row r="138" ht="180.35" customHeight="1">
+      <c r="B137" s="38">
+        <v>2</v>
+      </c>
+      <c r="C137" s="38">
+        <v>200</v>
+      </c>
+      <c r="D137" s="24"/>
+      <c r="E137" s="23"/>
+      <c r="F137" s="38">
+        <v>2</v>
+      </c>
+      <c r="G137" s="50">
+        <v>200</v>
+      </c>
+      <c r="H137" s="51"/>
+      <c r="I137" s="35"/>
+    </row>
+    <row r="138" ht="15.35" customHeight="1">
       <c r="A138" s="5"/>
-      <c r="B138" t="s" s="25">
-        <v>314</v>
-      </c>
-      <c r="C138" t="s" s="47">
-        <v>315</v>
-      </c>
-      <c r="D138" s="48"/>
-      <c r="E138" s="22"/>
-      <c r="F138" t="s" s="25">
-        <v>314</v>
-      </c>
-      <c r="G138" t="s" s="47">
-        <v>315</v>
-      </c>
-      <c r="H138" s="48"/>
-      <c r="I138" s="34"/>
+      <c r="B138" s="38">
+        <v>3</v>
+      </c>
+      <c r="C138" s="38">
+        <v>300</v>
+      </c>
+      <c r="D138" s="24"/>
+      <c r="E138" s="23"/>
+      <c r="F138" s="38">
+        <v>3</v>
+      </c>
+      <c r="G138" s="38">
+        <v>300</v>
+      </c>
+      <c r="H138" s="24"/>
+      <c r="I138" s="35"/>
     </row>
     <row r="139" ht="15.35" customHeight="1">
-      <c r="A139" s="5"/>
-      <c r="B139" t="s" s="25">
-        <v>316</v>
-      </c>
-      <c r="C139" t="s" s="25">
-        <v>317</v>
-      </c>
-      <c r="D139" s="23"/>
-      <c r="E139" s="22"/>
-      <c r="F139" t="s" s="25">
-        <v>316</v>
-      </c>
-      <c r="G139" t="s" s="25">
-        <v>317</v>
-      </c>
-      <c r="H139" s="23"/>
-      <c r="I139" s="34"/>
+      <c r="A139" s="2"/>
+      <c r="B139" s="32"/>
+      <c r="C139" s="32"/>
+      <c r="D139" s="32"/>
+      <c r="E139" s="2"/>
+      <c r="F139" s="32"/>
+      <c r="G139" s="32"/>
+      <c r="H139" s="32"/>
+      <c r="I139" s="2"/>
     </row>
     <row r="140" ht="15.35" customHeight="1">
-      <c r="A140" s="5"/>
-      <c r="B140" t="s" s="25">
-        <v>318</v>
-      </c>
-      <c r="C140" t="s" s="25">
-        <v>319</v>
-      </c>
-      <c r="D140" s="23"/>
-      <c r="E140" s="22"/>
-      <c r="F140" t="s" s="25">
-        <v>318</v>
-      </c>
-      <c r="G140" t="s" s="25">
-        <v>319</v>
-      </c>
-      <c r="H140" s="23"/>
-      <c r="I140" s="34"/>
+      <c r="A140" s="2"/>
+      <c r="B140" s="2"/>
+      <c r="C140" s="2"/>
+      <c r="D140" s="2"/>
+      <c r="E140" s="2"/>
+      <c r="F140" s="2"/>
+      <c r="G140" s="2"/>
+      <c r="H140" s="2"/>
+      <c r="I140" s="2"/>
     </row>
     <row r="141" ht="15.35" customHeight="1">
-      <c r="A141" s="5"/>
-      <c r="B141" s="37">
-        <v>1</v>
-      </c>
-      <c r="C141" s="37">
-        <v>100</v>
-      </c>
-      <c r="D141" s="23"/>
-      <c r="E141" s="22"/>
-      <c r="F141" s="37">
-        <v>1</v>
-      </c>
-      <c r="G141" s="49">
-        <v>100</v>
-      </c>
-      <c r="H141" s="50"/>
-      <c r="I141" s="34"/>
+      <c r="A141" s="2"/>
+      <c r="B141" s="2"/>
+      <c r="C141" s="2"/>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2"/>
+      <c r="F141" s="2"/>
+      <c r="G141" s="2"/>
+      <c r="H141" s="2"/>
+      <c r="I141" s="2"/>
     </row>
     <row r="142" ht="15.35" customHeight="1">
-      <c r="A142" s="5"/>
-      <c r="B142" s="37">
-        <v>2</v>
-      </c>
-      <c r="C142" s="37">
-        <v>200</v>
-      </c>
-      <c r="D142" s="23"/>
-      <c r="E142" s="22"/>
-      <c r="F142" s="37">
-        <v>2</v>
-      </c>
-      <c r="G142" s="49">
-        <v>200</v>
-      </c>
-      <c r="H142" s="50"/>
-      <c r="I142" s="34"/>
+      <c r="A142" s="2"/>
+      <c r="B142" s="4"/>
+      <c r="C142" s="4"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="2"/>
+      <c r="F142" s="2"/>
+      <c r="G142" s="2"/>
+      <c r="H142" s="2"/>
+      <c r="I142" s="2"/>
     </row>
     <row r="143" ht="15.35" customHeight="1">
       <c r="A143" s="5"/>
-      <c r="B143" s="37">
-        <v>3</v>
-      </c>
-      <c r="C143" s="37">
-        <v>300</v>
-      </c>
-      <c r="D143" s="23"/>
-      <c r="E143" s="22"/>
-      <c r="F143" s="37">
-        <v>3</v>
-      </c>
-      <c r="G143" s="37">
-        <v>300</v>
-      </c>
-      <c r="H143" s="23"/>
-      <c r="I143" s="34"/>
+      <c r="B143" t="s" s="52">
+        <v>311</v>
+      </c>
+      <c r="C143" s="53"/>
+      <c r="D143" s="53"/>
+      <c r="E143" s="54"/>
+      <c r="F143" s="2"/>
+      <c r="G143" s="2"/>
+      <c r="H143" s="2"/>
+      <c r="I143" s="2"/>
     </row>
     <row r="144" ht="15.35" customHeight="1">
-      <c r="A144" s="2"/>
-      <c r="B144" s="31"/>
-      <c r="C144" s="31"/>
-      <c r="D144" s="31"/>
-      <c r="E144" s="2"/>
-      <c r="F144" s="31"/>
-      <c r="G144" s="31"/>
-      <c r="H144" s="31"/>
+      <c r="A144" s="5"/>
+      <c r="B144" t="s" s="13">
+        <v>305</v>
+      </c>
+      <c r="C144" t="s" s="13">
+        <v>312</v>
+      </c>
+      <c r="D144" s="38">
+        <v>1</v>
+      </c>
+      <c r="E144" s="35"/>
+      <c r="F144" s="2"/>
+      <c r="G144" s="2"/>
+      <c r="H144" s="2"/>
       <c r="I144" s="2"/>
     </row>
     <row r="145" ht="15.35" customHeight="1">
-      <c r="A145" s="2"/>
-      <c r="B145" s="2"/>
-      <c r="C145" s="2"/>
-      <c r="D145" s="2"/>
-      <c r="E145" s="2"/>
+      <c r="A145" s="5"/>
+      <c r="B145" t="s" s="13">
+        <v>172</v>
+      </c>
+      <c r="C145" t="s" s="13">
+        <v>172</v>
+      </c>
+      <c r="D145" t="s" s="26">
+        <v>173</v>
+      </c>
+      <c r="E145" s="35"/>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
       <c r="I145" s="2"/>
     </row>
     <row r="146" ht="15.35" customHeight="1">
-      <c r="A146" s="2"/>
-      <c r="B146" s="2"/>
-      <c r="C146" s="2"/>
-      <c r="D146" s="2"/>
-      <c r="E146" s="2"/>
+      <c r="A146" s="5"/>
+      <c r="B146" t="s" s="13">
+        <v>313</v>
+      </c>
+      <c r="C146" t="s" s="13">
+        <v>314</v>
+      </c>
+      <c r="D146" t="b" s="38">
+        <v>1</v>
+      </c>
+      <c r="E146" s="35"/>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
       <c r="I146" s="2"/>
     </row>
     <row r="147" ht="15.35" customHeight="1">
-      <c r="A147" s="2"/>
-      <c r="B147" s="4"/>
-      <c r="C147" s="4"/>
-      <c r="D147" s="4"/>
-      <c r="E147" s="2"/>
+      <c r="A147" s="5"/>
+      <c r="B147" t="s" s="13">
+        <v>315</v>
+      </c>
+      <c r="C147" t="s" s="13">
+        <v>316</v>
+      </c>
+      <c r="D147" t="s" s="26">
+        <v>297</v>
+      </c>
+      <c r="E147" s="35"/>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
@@ -5617,12 +5561,16 @@
     </row>
     <row r="148" ht="15.35" customHeight="1">
       <c r="A148" s="5"/>
-      <c r="B148" t="s" s="51">
-        <v>320</v>
-      </c>
-      <c r="C148" s="52"/>
-      <c r="D148" s="52"/>
-      <c r="E148" s="53"/>
+      <c r="B148" t="s" s="13">
+        <v>317</v>
+      </c>
+      <c r="C148" t="s" s="13">
+        <v>318</v>
+      </c>
+      <c r="D148" t="b" s="38">
+        <v>1</v>
+      </c>
+      <c r="E148" s="35"/>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
@@ -5631,15 +5579,15 @@
     <row r="149" ht="15.35" customHeight="1">
       <c r="A149" s="5"/>
       <c r="B149" t="s" s="13">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C149" t="s" s="13">
-        <v>321</v>
-      </c>
-      <c r="D149" s="37">
-        <v>1</v>
-      </c>
-      <c r="E149" s="34"/>
+        <v>320</v>
+      </c>
+      <c r="D149" t="s" s="26">
+        <v>300</v>
+      </c>
+      <c r="E149" s="35"/>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
@@ -5648,15 +5596,15 @@
     <row r="150" ht="15.35" customHeight="1">
       <c r="A150" s="5"/>
       <c r="B150" t="s" s="13">
-        <v>177</v>
+        <v>321</v>
       </c>
       <c r="C150" t="s" s="13">
-        <v>177</v>
-      </c>
-      <c r="D150" t="s" s="25">
-        <v>178</v>
-      </c>
-      <c r="E150" s="34"/>
+        <v>322</v>
+      </c>
+      <c r="D150" t="s" s="26">
+        <v>6</v>
+      </c>
+      <c r="E150" s="35"/>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
@@ -5665,15 +5613,15 @@
     <row r="151" ht="15.35" customHeight="1">
       <c r="A151" s="5"/>
       <c r="B151" t="s" s="13">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C151" t="s" s="13">
-        <v>323</v>
-      </c>
-      <c r="D151" t="b" s="37">
-        <v>1</v>
-      </c>
-      <c r="E151" s="34"/>
+        <v>324</v>
+      </c>
+      <c r="D151" t="s" s="26">
+        <v>301</v>
+      </c>
+      <c r="E151" s="35"/>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
@@ -5682,15 +5630,15 @@
     <row r="152" ht="15.35" customHeight="1">
       <c r="A152" s="5"/>
       <c r="B152" t="s" s="13">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C152" t="s" s="13">
-        <v>325</v>
-      </c>
-      <c r="D152" t="b" s="37">
-        <v>1</v>
-      </c>
-      <c r="E152" s="34"/>
+        <v>326</v>
+      </c>
+      <c r="D152" t="s" s="26">
+        <v>42</v>
+      </c>
+      <c r="E152" s="35"/>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
@@ -5699,15 +5647,15 @@
     <row r="153" ht="15.35" customHeight="1">
       <c r="A153" s="5"/>
       <c r="B153" t="s" s="13">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C153" t="s" s="13">
-        <v>327</v>
-      </c>
-      <c r="D153" t="s" s="25">
-        <v>306</v>
-      </c>
-      <c r="E153" s="34"/>
+        <v>328</v>
+      </c>
+      <c r="D153" s="39">
+        <v>45209</v>
+      </c>
+      <c r="E153" s="35"/>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
@@ -5716,15 +5664,15 @@
     <row r="154" ht="15.35" customHeight="1">
       <c r="A154" s="5"/>
       <c r="B154" t="s" s="13">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C154" t="s" s="13">
-        <v>329</v>
-      </c>
-      <c r="D154" t="b" s="37">
-        <v>1</v>
-      </c>
-      <c r="E154" s="34"/>
+        <v>330</v>
+      </c>
+      <c r="D154" t="b" s="38">
+        <v>0</v>
+      </c>
+      <c r="E154" s="35"/>
       <c r="F154" s="2"/>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
@@ -5733,15 +5681,15 @@
     <row r="155" ht="15.35" customHeight="1">
       <c r="A155" s="5"/>
       <c r="B155" t="s" s="13">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C155" t="s" s="13">
-        <v>331</v>
-      </c>
-      <c r="D155" t="s" s="25">
-        <v>309</v>
-      </c>
-      <c r="E155" s="34"/>
+        <v>332</v>
+      </c>
+      <c r="D155" t="s" s="26">
+        <v>298</v>
+      </c>
+      <c r="E155" s="35"/>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
@@ -5750,15 +5698,15 @@
     <row r="156" ht="15.35" customHeight="1">
       <c r="A156" s="5"/>
       <c r="B156" t="s" s="13">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C156" t="s" s="13">
-        <v>333</v>
-      </c>
-      <c r="D156" t="s" s="25">
-        <v>6</v>
-      </c>
-      <c r="E156" s="34"/>
+        <v>334</v>
+      </c>
+      <c r="D156" t="b" s="38">
+        <v>0</v>
+      </c>
+      <c r="E156" s="35"/>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
@@ -5767,15 +5715,15 @@
     <row r="157" ht="15.35" customHeight="1">
       <c r="A157" s="5"/>
       <c r="B157" t="s" s="13">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C157" t="s" s="13">
-        <v>335</v>
-      </c>
-      <c r="D157" t="s" s="25">
-        <v>310</v>
-      </c>
-      <c r="E157" s="34"/>
+        <v>336</v>
+      </c>
+      <c r="D157" t="s" s="26">
+        <v>300</v>
+      </c>
+      <c r="E157" s="35"/>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
@@ -5784,15 +5732,15 @@
     <row r="158" ht="15.35" customHeight="1">
       <c r="A158" s="5"/>
       <c r="B158" t="s" s="13">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C158" t="s" s="13">
-        <v>337</v>
-      </c>
-      <c r="D158" t="s" s="25">
-        <v>43</v>
-      </c>
-      <c r="E158" s="34"/>
+        <v>338</v>
+      </c>
+      <c r="D158" t="s" s="26">
+        <v>7</v>
+      </c>
+      <c r="E158" s="35"/>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
@@ -5801,15 +5749,15 @@
     <row r="159" ht="15.35" customHeight="1">
       <c r="A159" s="5"/>
       <c r="B159" t="s" s="13">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C159" t="s" s="13">
-        <v>339</v>
-      </c>
-      <c r="D159" s="38">
-        <v>45209</v>
-      </c>
-      <c r="E159" s="34"/>
+        <v>340</v>
+      </c>
+      <c r="D159" t="s" s="26">
+        <v>302</v>
+      </c>
+      <c r="E159" s="35"/>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
@@ -5818,15 +5766,15 @@
     <row r="160" ht="15.35" customHeight="1">
       <c r="A160" s="5"/>
       <c r="B160" t="s" s="13">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C160" t="s" s="13">
-        <v>341</v>
-      </c>
-      <c r="D160" t="b" s="37">
-        <v>0</v>
-      </c>
-      <c r="E160" s="34"/>
+        <v>342</v>
+      </c>
+      <c r="D160" t="s" s="26">
+        <v>343</v>
+      </c>
+      <c r="E160" s="35"/>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
@@ -5835,15 +5783,15 @@
     <row r="161" ht="15.35" customHeight="1">
       <c r="A161" s="5"/>
       <c r="B161" t="s" s="13">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C161" t="s" s="13">
-        <v>343</v>
-      </c>
-      <c r="D161" t="b" s="37">
-        <v>0</v>
-      </c>
-      <c r="E161" s="34"/>
+        <v>345</v>
+      </c>
+      <c r="D161" s="39">
+        <v>45240</v>
+      </c>
+      <c r="E161" s="35"/>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
@@ -5852,15 +5800,15 @@
     <row r="162" ht="15.35" customHeight="1">
       <c r="A162" s="5"/>
       <c r="B162" t="s" s="13">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C162" t="s" s="13">
-        <v>345</v>
-      </c>
-      <c r="D162" t="s" s="25">
-        <v>307</v>
-      </c>
-      <c r="E162" s="34"/>
+        <v>347</v>
+      </c>
+      <c r="D162" t="b" s="38">
+        <v>0</v>
+      </c>
+      <c r="E162" s="35"/>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
@@ -5869,15 +5817,15 @@
     <row r="163" ht="15.35" customHeight="1">
       <c r="A163" s="5"/>
       <c r="B163" t="s" s="13">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C163" t="s" s="13">
-        <v>347</v>
-      </c>
-      <c r="D163" t="b" s="37">
-        <v>0</v>
-      </c>
-      <c r="E163" s="34"/>
+        <v>349</v>
+      </c>
+      <c r="D163" t="s" s="26">
+        <v>298</v>
+      </c>
+      <c r="E163" s="35"/>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
@@ -5886,15 +5834,15 @@
     <row r="164" ht="15.35" customHeight="1">
       <c r="A164" s="5"/>
       <c r="B164" t="s" s="13">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C164" t="s" s="13">
-        <v>349</v>
-      </c>
-      <c r="D164" t="s" s="25">
-        <v>309</v>
-      </c>
-      <c r="E164" s="34"/>
+        <v>351</v>
+      </c>
+      <c r="D164" t="b" s="38">
+        <v>0</v>
+      </c>
+      <c r="E164" s="35"/>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
@@ -5903,15 +5851,15 @@
     <row r="165" ht="15.35" customHeight="1">
       <c r="A165" s="5"/>
       <c r="B165" t="s" s="13">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C165" t="s" s="13">
-        <v>351</v>
-      </c>
-      <c r="D165" t="s" s="25">
-        <v>7</v>
-      </c>
-      <c r="E165" s="34"/>
+        <v>353</v>
+      </c>
+      <c r="D165" t="s" s="26">
+        <v>300</v>
+      </c>
+      <c r="E165" s="35"/>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
@@ -5920,15 +5868,15 @@
     <row r="166" ht="15.35" customHeight="1">
       <c r="A166" s="5"/>
       <c r="B166" t="s" s="13">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C166" t="s" s="13">
-        <v>353</v>
-      </c>
-      <c r="D166" t="s" s="25">
-        <v>311</v>
-      </c>
-      <c r="E166" s="34"/>
+        <v>355</v>
+      </c>
+      <c r="D166" t="s" s="26">
+        <v>356</v>
+      </c>
+      <c r="E166" s="35"/>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
@@ -5937,15 +5885,15 @@
     <row r="167" ht="15.35" customHeight="1">
       <c r="A167" s="5"/>
       <c r="B167" t="s" s="13">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C167" t="s" s="13">
-        <v>355</v>
-      </c>
-      <c r="D167" t="s" s="25">
-        <v>356</v>
-      </c>
-      <c r="E167" s="34"/>
+        <v>358</v>
+      </c>
+      <c r="D167" t="s" s="26">
+        <v>359</v>
+      </c>
+      <c r="E167" s="35"/>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
@@ -5954,15 +5902,15 @@
     <row r="168" ht="15.35" customHeight="1">
       <c r="A168" s="5"/>
       <c r="B168" t="s" s="13">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C168" t="s" s="13">
-        <v>358</v>
-      </c>
-      <c r="D168" s="38">
-        <v>45240</v>
-      </c>
-      <c r="E168" s="34"/>
+        <v>361</v>
+      </c>
+      <c r="D168" t="s" s="26">
+        <v>293</v>
+      </c>
+      <c r="E168" s="35"/>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
@@ -5971,161 +5919,115 @@
     <row r="169" ht="15.35" customHeight="1">
       <c r="A169" s="5"/>
       <c r="B169" t="s" s="13">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C169" t="s" s="13">
-        <v>360</v>
-      </c>
-      <c r="D169" t="b" s="37">
-        <v>0</v>
-      </c>
-      <c r="E169" s="34"/>
+        <v>363</v>
+      </c>
+      <c r="D169" s="39">
+        <v>45240</v>
+      </c>
+      <c r="E169" s="35"/>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
     </row>
     <row r="170" ht="15.35" customHeight="1">
-      <c r="A170" s="5"/>
-      <c r="B170" t="s" s="13">
-        <v>361</v>
-      </c>
-      <c r="C170" t="s" s="13">
-        <v>362</v>
-      </c>
-      <c r="D170" t="b" s="37">
-        <v>1</v>
-      </c>
-      <c r="E170" s="34"/>
+      <c r="A170" s="2"/>
+      <c r="B170" s="32"/>
+      <c r="C170" s="32"/>
+      <c r="D170" s="32"/>
+      <c r="E170" s="2"/>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
     </row>
     <row r="171" ht="15.35" customHeight="1">
-      <c r="A171" s="5"/>
-      <c r="B171" t="s" s="13">
-        <v>363</v>
-      </c>
-      <c r="C171" t="s" s="13">
-        <v>364</v>
-      </c>
-      <c r="D171" t="s" s="25">
-        <v>307</v>
-      </c>
-      <c r="E171" s="34"/>
+      <c r="A171" s="2"/>
+      <c r="B171" s="2"/>
+      <c r="C171" s="2"/>
+      <c r="D171" s="2"/>
+      <c r="E171" s="2"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
     </row>
     <row r="172" ht="15.35" customHeight="1">
-      <c r="A172" s="5"/>
-      <c r="B172" t="s" s="13">
-        <v>365</v>
-      </c>
-      <c r="C172" t="s" s="13">
-        <v>366</v>
-      </c>
-      <c r="D172" t="b" s="37">
-        <v>0</v>
-      </c>
-      <c r="E172" s="34"/>
+      <c r="A172" s="2"/>
+      <c r="B172" s="2"/>
+      <c r="C172" s="2"/>
+      <c r="D172" s="2"/>
+      <c r="E172" s="2"/>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
     </row>
     <row r="173" ht="15.35" customHeight="1">
-      <c r="A173" s="5"/>
-      <c r="B173" t="s" s="13">
-        <v>367</v>
-      </c>
-      <c r="C173" t="s" s="13">
-        <v>368</v>
-      </c>
-      <c r="D173" t="s" s="25">
-        <v>309</v>
-      </c>
-      <c r="E173" s="34"/>
+      <c r="A173" s="2"/>
+      <c r="B173" s="2"/>
+      <c r="C173" s="2"/>
+      <c r="D173" s="2"/>
+      <c r="E173" s="2"/>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
     </row>
     <row r="174" ht="15.35" customHeight="1">
-      <c r="A174" s="5"/>
-      <c r="B174" t="s" s="13">
-        <v>369</v>
-      </c>
-      <c r="C174" t="s" s="13">
-        <v>370</v>
-      </c>
-      <c r="D174" t="s" s="25">
-        <v>371</v>
-      </c>
-      <c r="E174" s="34"/>
+      <c r="A174" s="2"/>
+      <c r="B174" s="2"/>
+      <c r="C174" s="2"/>
+      <c r="D174" s="2"/>
+      <c r="E174" s="2"/>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
     </row>
     <row r="175" ht="15.35" customHeight="1">
-      <c r="A175" s="5"/>
-      <c r="B175" t="s" s="13">
-        <v>372</v>
-      </c>
-      <c r="C175" t="s" s="13">
-        <v>373</v>
-      </c>
-      <c r="D175" t="s" s="25">
-        <v>374</v>
-      </c>
-      <c r="E175" s="34"/>
+      <c r="A175" s="2"/>
+      <c r="B175" s="2"/>
+      <c r="C175" s="2"/>
+      <c r="D175" s="2"/>
+      <c r="E175" s="2"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
     </row>
     <row r="176" ht="15.35" customHeight="1">
-      <c r="A176" s="5"/>
-      <c r="B176" t="s" s="13">
-        <v>375</v>
-      </c>
-      <c r="C176" t="s" s="13">
-        <v>376</v>
-      </c>
-      <c r="D176" t="s" s="25">
-        <v>302</v>
-      </c>
-      <c r="E176" s="34"/>
+      <c r="A176" s="2"/>
+      <c r="B176" s="2"/>
+      <c r="C176" s="2"/>
+      <c r="D176" s="2"/>
+      <c r="E176" s="2"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
       <c r="I176" s="2"/>
     </row>
     <row r="177" ht="15.35" customHeight="1">
-      <c r="A177" s="5"/>
-      <c r="B177" t="s" s="13">
-        <v>377</v>
-      </c>
-      <c r="C177" t="s" s="13">
-        <v>378</v>
-      </c>
-      <c r="D177" s="38">
-        <v>45240</v>
-      </c>
-      <c r="E177" s="34"/>
+      <c r="A177" s="2"/>
+      <c r="B177" s="4"/>
+      <c r="C177" s="4"/>
+      <c r="D177" s="2"/>
+      <c r="E177" s="2"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
       <c r="I177" s="2"/>
     </row>
     <row r="178" ht="15.35" customHeight="1">
-      <c r="A178" s="2"/>
-      <c r="B178" s="31"/>
-      <c r="C178" s="31"/>
-      <c r="D178" s="31"/>
+      <c r="A178" s="5"/>
+      <c r="B178" t="s" s="52">
+        <v>364</v>
+      </c>
+      <c r="C178" s="53"/>
+      <c r="D178" s="35"/>
       <c r="E178" s="2"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
@@ -6133,10 +6035,14 @@
       <c r="I178" s="2"/>
     </row>
     <row r="179" ht="15.35" customHeight="1">
-      <c r="A179" s="2"/>
-      <c r="B179" s="2"/>
-      <c r="C179" s="2"/>
-      <c r="D179" s="2"/>
+      <c r="A179" s="5"/>
+      <c r="B179" t="s" s="26">
+        <v>365</v>
+      </c>
+      <c r="C179" t="s" s="26">
+        <v>366</v>
+      </c>
+      <c r="D179" s="35"/>
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
@@ -6145,8 +6051,8 @@
     </row>
     <row r="180" ht="15.35" customHeight="1">
       <c r="A180" s="2"/>
-      <c r="B180" s="2"/>
-      <c r="C180" s="2"/>
+      <c r="B180" s="32"/>
+      <c r="C180" s="32"/>
       <c r="D180" s="2"/>
       <c r="E180" s="2"/>
       <c r="F180" s="2"/>
@@ -6156,8 +6062,8 @@
     </row>
     <row r="181" ht="15.35" customHeight="1">
       <c r="A181" s="2"/>
-      <c r="B181" s="2"/>
-      <c r="C181" s="2"/>
+      <c r="B181" s="4"/>
+      <c r="C181" s="4"/>
       <c r="D181" s="2"/>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
@@ -6166,10 +6072,12 @@
       <c r="I181" s="2"/>
     </row>
     <row r="182" ht="15.35" customHeight="1">
-      <c r="A182" s="2"/>
-      <c r="B182" s="2"/>
-      <c r="C182" s="2"/>
-      <c r="D182" s="2"/>
+      <c r="A182" s="5"/>
+      <c r="B182" t="s" s="52">
+        <v>51</v>
+      </c>
+      <c r="C182" s="53"/>
+      <c r="D182" s="35"/>
       <c r="E182" s="2"/>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
@@ -6177,10 +6085,14 @@
       <c r="I182" s="2"/>
     </row>
     <row r="183" ht="15.35" customHeight="1">
-      <c r="A183" s="2"/>
-      <c r="B183" s="2"/>
-      <c r="C183" s="2"/>
-      <c r="D183" s="2"/>
+      <c r="A183" s="5"/>
+      <c r="B183" t="s" s="26">
+        <v>367</v>
+      </c>
+      <c r="C183" t="s" s="26">
+        <v>368</v>
+      </c>
+      <c r="D183" s="35"/>
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
@@ -6188,10 +6100,14 @@
       <c r="I183" s="2"/>
     </row>
     <row r="184" ht="15.35" customHeight="1">
-      <c r="A184" s="2"/>
-      <c r="B184" s="2"/>
-      <c r="C184" s="2"/>
-      <c r="D184" s="2"/>
+      <c r="A184" s="5"/>
+      <c r="B184" t="s" s="26">
+        <v>41</v>
+      </c>
+      <c r="C184" t="s" s="26">
+        <v>343</v>
+      </c>
+      <c r="D184" s="35"/>
       <c r="E184" s="2"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
@@ -6200,8 +6116,8 @@
     </row>
     <row r="185" ht="15.35" customHeight="1">
       <c r="A185" s="2"/>
-      <c r="B185" s="4"/>
-      <c r="C185" s="4"/>
+      <c r="B185" s="32"/>
+      <c r="C185" s="32"/>
       <c r="D185" s="2"/>
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
@@ -6210,12 +6126,10 @@
       <c r="I185" s="2"/>
     </row>
     <row r="186" ht="15.35" customHeight="1">
-      <c r="A186" s="5"/>
-      <c r="B186" t="s" s="51">
-        <v>379</v>
-      </c>
-      <c r="C186" s="52"/>
-      <c r="D186" s="34"/>
+      <c r="A186" s="2"/>
+      <c r="B186" s="2"/>
+      <c r="C186" s="2"/>
+      <c r="D186" s="2"/>
       <c r="E186" s="2"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
@@ -6223,14 +6137,12 @@
       <c r="I186" s="2"/>
     </row>
     <row r="187" ht="15.35" customHeight="1">
-      <c r="A187" s="5"/>
-      <c r="B187" t="s" s="25">
-        <v>380</v>
-      </c>
-      <c r="C187" t="s" s="25">
-        <v>381</v>
-      </c>
-      <c r="D187" s="34"/>
+      <c r="A187" s="2"/>
+      <c r="B187" t="s" s="55">
+        <v>369</v>
+      </c>
+      <c r="C187" s="2"/>
+      <c r="D187" s="2"/>
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
@@ -6239,8 +6151,8 @@
     </row>
     <row r="188" ht="15.35" customHeight="1">
       <c r="A188" s="2"/>
-      <c r="B188" s="31"/>
-      <c r="C188" s="31"/>
+      <c r="B188" s="2"/>
+      <c r="C188" s="2"/>
       <c r="D188" s="2"/>
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
@@ -6252,7 +6164,7 @@
       <c r="A189" s="2"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
-      <c r="D189" s="2"/>
+      <c r="D189" s="4"/>
       <c r="E189" s="2"/>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
@@ -6261,12 +6173,12 @@
     </row>
     <row r="190" ht="15.35" customHeight="1">
       <c r="A190" s="5"/>
-      <c r="B190" t="s" s="51">
-        <v>52</v>
-      </c>
-      <c r="C190" s="52"/>
-      <c r="D190" s="34"/>
-      <c r="E190" s="2"/>
+      <c r="B190" t="s" s="52">
+        <v>370</v>
+      </c>
+      <c r="C190" s="53"/>
+      <c r="D190" s="53"/>
+      <c r="E190" s="35"/>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
@@ -6274,14 +6186,16 @@
     </row>
     <row r="191" ht="15.35" customHeight="1">
       <c r="A191" s="5"/>
-      <c r="B191" t="s" s="25">
-        <v>382</v>
-      </c>
-      <c r="C191" t="s" s="25">
-        <v>383</v>
-      </c>
-      <c r="D191" s="34"/>
-      <c r="E191" s="2"/>
+      <c r="B191" t="s" s="56">
+        <v>1</v>
+      </c>
+      <c r="C191" t="s" s="57">
+        <v>30</v>
+      </c>
+      <c r="D191" t="s" s="58">
+        <v>371</v>
+      </c>
+      <c r="E191" s="35"/>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
@@ -6289,135 +6203,145 @@
     </row>
     <row r="192" ht="15.35" customHeight="1">
       <c r="A192" s="5"/>
-      <c r="B192" t="s" s="25">
-        <v>42</v>
-      </c>
-      <c r="C192" t="s" s="25">
-        <v>356</v>
-      </c>
-      <c r="D192" s="34"/>
-      <c r="E192" s="2"/>
+      <c r="B192" t="s" s="13">
+        <v>303</v>
+      </c>
+      <c r="C192" t="s" s="13">
+        <v>372</v>
+      </c>
+      <c r="D192" t="s" s="13">
+        <v>304</v>
+      </c>
+      <c r="E192" s="35"/>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
     </row>
     <row r="193" ht="15.35" customHeight="1">
-      <c r="A193" s="2"/>
-      <c r="B193" s="31"/>
-      <c r="C193" s="31"/>
-      <c r="D193" s="2"/>
-      <c r="E193" s="2"/>
+      <c r="A193" s="5"/>
+      <c r="B193" t="s" s="13">
+        <v>373</v>
+      </c>
+      <c r="C193" t="s" s="13">
+        <v>374</v>
+      </c>
+      <c r="D193" t="s" s="13">
+        <v>375</v>
+      </c>
+      <c r="E193" s="35"/>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
       <c r="I193" s="2"/>
     </row>
     <row r="194" ht="15.35" customHeight="1">
-      <c r="A194" s="2"/>
-      <c r="B194" s="2"/>
-      <c r="C194" s="2"/>
-      <c r="D194" s="2"/>
-      <c r="E194" s="2"/>
+      <c r="A194" s="5"/>
+      <c r="B194" t="s" s="13">
+        <v>376</v>
+      </c>
+      <c r="C194" t="s" s="13">
+        <v>377</v>
+      </c>
+      <c r="D194" t="s" s="13">
+        <v>378</v>
+      </c>
+      <c r="E194" s="35"/>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
     </row>
     <row r="195" ht="15.35" customHeight="1">
-      <c r="A195" s="2"/>
-      <c r="B195" t="s" s="54">
-        <v>384</v>
-      </c>
-      <c r="C195" s="2"/>
-      <c r="D195" s="2"/>
-      <c r="E195" s="2"/>
+      <c r="A195" s="5"/>
+      <c r="B195" t="s" s="13">
+        <v>379</v>
+      </c>
+      <c r="C195" t="s" s="13">
+        <v>380</v>
+      </c>
+      <c r="D195" t="s" s="13">
+        <v>54</v>
+      </c>
+      <c r="E195" s="35"/>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
       <c r="I195" s="2"/>
     </row>
     <row r="196" ht="15.35" customHeight="1">
-      <c r="A196" s="2"/>
-      <c r="B196" s="2"/>
-      <c r="C196" s="2"/>
-      <c r="D196" s="2"/>
-      <c r="E196" s="2"/>
+      <c r="A196" s="5"/>
+      <c r="B196" t="s" s="26">
+        <v>381</v>
+      </c>
+      <c r="C196" t="s" s="26">
+        <v>382</v>
+      </c>
+      <c r="D196" t="s" s="26">
+        <v>383</v>
+      </c>
+      <c r="E196" s="35"/>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
       <c r="I196" s="2"/>
     </row>
     <row r="197" ht="15.35" customHeight="1">
-      <c r="A197" s="2"/>
-      <c r="B197" s="4"/>
-      <c r="C197" s="4"/>
-      <c r="D197" s="4"/>
-      <c r="E197" s="2"/>
+      <c r="A197" s="5"/>
+      <c r="B197" t="s" s="26">
+        <v>384</v>
+      </c>
+      <c r="C197" t="s" s="26">
+        <v>382</v>
+      </c>
+      <c r="D197" t="s" s="26">
+        <v>382</v>
+      </c>
+      <c r="E197" s="35"/>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
       <c r="I197" s="2"/>
     </row>
     <row r="198" ht="15.35" customHeight="1">
-      <c r="A198" s="5"/>
-      <c r="B198" t="s" s="51">
-        <v>385</v>
-      </c>
-      <c r="C198" s="52"/>
-      <c r="D198" s="52"/>
-      <c r="E198" s="34"/>
+      <c r="A198" s="2"/>
+      <c r="B198" s="32"/>
+      <c r="C198" s="32"/>
+      <c r="D198" s="32"/>
+      <c r="E198" s="2"/>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
       <c r="I198" s="2"/>
     </row>
     <row r="199" ht="15.35" customHeight="1">
-      <c r="A199" s="5"/>
-      <c r="B199" t="s" s="55">
-        <v>1</v>
-      </c>
-      <c r="C199" t="s" s="56">
-        <v>31</v>
-      </c>
-      <c r="D199" t="s" s="57">
-        <v>386</v>
-      </c>
-      <c r="E199" s="34"/>
+      <c r="A199" s="2"/>
+      <c r="B199" s="2"/>
+      <c r="C199" s="2"/>
+      <c r="D199" s="2"/>
+      <c r="E199" s="2"/>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
     </row>
     <row r="200" ht="15.35" customHeight="1">
-      <c r="A200" s="5"/>
-      <c r="B200" t="s" s="13">
-        <v>312</v>
-      </c>
-      <c r="C200" t="s" s="13">
-        <v>387</v>
-      </c>
-      <c r="D200" t="s" s="13">
-        <v>313</v>
-      </c>
-      <c r="E200" s="34"/>
+      <c r="A200" s="2"/>
+      <c r="B200" s="2"/>
+      <c r="C200" s="2"/>
+      <c r="D200" s="2"/>
+      <c r="E200" s="2"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>
     </row>
     <row r="201" ht="15.35" customHeight="1">
-      <c r="A201" s="5"/>
-      <c r="B201" t="s" s="13">
-        <v>388</v>
-      </c>
-      <c r="C201" t="s" s="13">
-        <v>389</v>
-      </c>
-      <c r="D201" t="s" s="13">
-        <v>390</v>
-      </c>
-      <c r="E201" s="34"/>
+      <c r="A201" s="2"/>
+      <c r="B201" s="4"/>
+      <c r="C201" s="4"/>
+      <c r="D201" s="2"/>
+      <c r="E201" s="2"/>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
@@ -6425,16 +6349,12 @@
     </row>
     <row r="202" ht="15.35" customHeight="1">
       <c r="A202" s="5"/>
-      <c r="B202" t="s" s="13">
-        <v>391</v>
-      </c>
-      <c r="C202" t="s" s="13">
-        <v>392</v>
-      </c>
-      <c r="D202" t="s" s="13">
-        <v>393</v>
-      </c>
-      <c r="E202" s="34"/>
+      <c r="B202" t="s" s="52">
+        <v>385</v>
+      </c>
+      <c r="C202" s="53"/>
+      <c r="D202" s="35"/>
+      <c r="E202" s="2"/>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
@@ -6443,15 +6363,13 @@
     <row r="203" ht="15.35" customHeight="1">
       <c r="A203" s="5"/>
       <c r="B203" t="s" s="13">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="C203" t="s" s="13">
-        <v>395</v>
-      </c>
-      <c r="D203" t="s" s="13">
-        <v>55</v>
-      </c>
-      <c r="E203" s="34"/>
+        <v>387</v>
+      </c>
+      <c r="D203" s="35"/>
+      <c r="E203" s="2"/>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
@@ -6459,16 +6377,14 @@
     </row>
     <row r="204" ht="15.35" customHeight="1">
       <c r="A204" s="5"/>
-      <c r="B204" t="s" s="25">
-        <v>396</v>
-      </c>
-      <c r="C204" t="s" s="25">
-        <v>397</v>
-      </c>
-      <c r="D204" t="s" s="25">
-        <v>398</v>
-      </c>
-      <c r="E204" s="34"/>
+      <c r="B204" t="s" s="13">
+        <v>388</v>
+      </c>
+      <c r="C204" t="s" s="13">
+        <v>389</v>
+      </c>
+      <c r="D204" s="35"/>
+      <c r="E204" s="2"/>
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
@@ -6476,195 +6392,90 @@
     </row>
     <row r="205" ht="15.35" customHeight="1">
       <c r="A205" s="5"/>
-      <c r="B205" t="s" s="25">
-        <v>399</v>
-      </c>
-      <c r="C205" t="s" s="25">
-        <v>397</v>
-      </c>
-      <c r="D205" t="s" s="25">
-        <v>397</v>
-      </c>
-      <c r="E205" s="34"/>
+      <c r="B205" t="b" s="38">
+        <v>1</v>
+      </c>
+      <c r="C205" t="s" s="26">
+        <v>390</v>
+      </c>
+      <c r="D205" s="35"/>
+      <c r="E205" s="2"/>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
       <c r="I205" s="2"/>
     </row>
     <row r="206" ht="15.35" customHeight="1">
-      <c r="A206" s="2"/>
-      <c r="B206" s="31"/>
-      <c r="C206" s="31"/>
-      <c r="D206" s="31"/>
+      <c r="A206" s="5"/>
+      <c r="B206" t="b" s="38">
+        <v>0</v>
+      </c>
+      <c r="C206" t="s" s="26">
+        <v>391</v>
+      </c>
+      <c r="D206" s="35"/>
       <c r="E206" s="2"/>
       <c r="F206" s="2"/>
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
       <c r="I206" s="2"/>
     </row>
-    <row r="207" ht="15.35" customHeight="1">
-      <c r="A207" s="2"/>
-      <c r="B207" s="2"/>
-      <c r="C207" s="2"/>
-      <c r="D207" s="2"/>
-      <c r="E207" s="2"/>
-      <c r="F207" s="2"/>
-      <c r="G207" s="2"/>
-      <c r="H207" s="2"/>
-      <c r="I207" s="2"/>
-    </row>
-    <row r="208" ht="15.35" customHeight="1">
-      <c r="A208" s="2"/>
-      <c r="B208" s="2"/>
-      <c r="C208" s="2"/>
-      <c r="D208" s="2"/>
-      <c r="E208" s="2"/>
-      <c r="F208" s="2"/>
-      <c r="G208" s="2"/>
-      <c r="H208" s="2"/>
-      <c r="I208" s="2"/>
-    </row>
-    <row r="209" ht="15.35" customHeight="1">
-      <c r="A209" s="2"/>
-      <c r="B209" s="4"/>
-      <c r="C209" s="4"/>
-      <c r="D209" s="2"/>
-      <c r="E209" s="2"/>
-      <c r="F209" s="2"/>
-      <c r="G209" s="2"/>
-      <c r="H209" s="2"/>
-      <c r="I209" s="2"/>
-    </row>
-    <row r="210" ht="15.35" customHeight="1">
-      <c r="A210" s="5"/>
-      <c r="B210" t="s" s="51">
-        <v>400</v>
-      </c>
-      <c r="C210" s="52"/>
-      <c r="D210" s="34"/>
-      <c r="E210" s="2"/>
-      <c r="F210" s="2"/>
-      <c r="G210" s="2"/>
-      <c r="H210" s="2"/>
-      <c r="I210" s="2"/>
-    </row>
-    <row r="211" ht="15.35" customHeight="1">
-      <c r="A211" s="5"/>
-      <c r="B211" t="s" s="13">
-        <v>401</v>
-      </c>
-      <c r="C211" t="s" s="13">
-        <v>402</v>
-      </c>
-      <c r="D211" s="34"/>
-      <c r="E211" s="2"/>
-      <c r="F211" s="2"/>
-      <c r="G211" s="2"/>
-      <c r="H211" s="2"/>
-      <c r="I211" s="2"/>
-    </row>
-    <row r="212" ht="15.35" customHeight="1">
-      <c r="A212" s="5"/>
-      <c r="B212" t="s" s="13">
-        <v>403</v>
-      </c>
-      <c r="C212" t="s" s="13">
-        <v>404</v>
-      </c>
-      <c r="D212" s="34"/>
-      <c r="E212" s="2"/>
-      <c r="F212" s="2"/>
-      <c r="G212" s="2"/>
-      <c r="H212" s="2"/>
-      <c r="I212" s="2"/>
-    </row>
-    <row r="213" ht="15.35" customHeight="1">
-      <c r="A213" s="5"/>
-      <c r="B213" t="b" s="37">
-        <v>1</v>
-      </c>
-      <c r="C213" t="s" s="25">
-        <v>405</v>
-      </c>
-      <c r="D213" s="34"/>
-      <c r="E213" s="2"/>
-      <c r="F213" s="2"/>
-      <c r="G213" s="2"/>
-      <c r="H213" s="2"/>
-      <c r="I213" s="2"/>
-    </row>
-    <row r="214" ht="15.35" customHeight="1">
-      <c r="A214" s="5"/>
-      <c r="B214" t="b" s="37">
-        <v>0</v>
-      </c>
-      <c r="C214" t="s" s="25">
-        <v>406</v>
-      </c>
-      <c r="D214" s="34"/>
-      <c r="E214" s="2"/>
-      <c r="F214" s="2"/>
-      <c r="G214" s="2"/>
-      <c r="H214" s="2"/>
-      <c r="I214" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="55">
-    <mergeCell ref="B210:C210"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="H53:I53"/>
+  <mergeCells count="54">
+    <mergeCell ref="B202:C202"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H45:I45"/>
     <mergeCell ref="H46:I46"/>
     <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H41:I41"/>
     <mergeCell ref="H48:I48"/>
     <mergeCell ref="H49:I49"/>
     <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H44:I44"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="G4:I4"/>
-    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H36:I36"/>
     <mergeCell ref="H37:I37"/>
     <mergeCell ref="H38:I38"/>
     <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="B5:B30"/>
-    <mergeCell ref="G5:G30"/>
+    <mergeCell ref="B5:B29"/>
+    <mergeCell ref="G5:G29"/>
+    <mergeCell ref="H30:I30"/>
     <mergeCell ref="H31:I31"/>
     <mergeCell ref="H32:I32"/>
     <mergeCell ref="H33:I33"/>
     <mergeCell ref="H34:I34"/>
     <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="B127:D127"/>
-    <mergeCell ref="B148:D148"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="B123:D123"/>
+    <mergeCell ref="B143:D143"/>
+    <mergeCell ref="C133:D133"/>
+    <mergeCell ref="C132:D132"/>
     <mergeCell ref="C138:D138"/>
     <mergeCell ref="C137:D137"/>
-    <mergeCell ref="C143:D143"/>
-    <mergeCell ref="C142:D142"/>
-    <mergeCell ref="C141:D141"/>
-    <mergeCell ref="B128:B136"/>
+    <mergeCell ref="C136:D136"/>
+    <mergeCell ref="B124:B131"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="H53:I53"/>
     <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H57:I57"/>
     <mergeCell ref="H55:I55"/>
     <mergeCell ref="H56:I56"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="B198:D198"/>
-    <mergeCell ref="B186:C186"/>
-    <mergeCell ref="B190:C190"/>
-    <mergeCell ref="C140:D140"/>
-    <mergeCell ref="C139:D139"/>
+    <mergeCell ref="B190:D190"/>
+    <mergeCell ref="B178:C178"/>
+    <mergeCell ref="B182:C182"/>
+    <mergeCell ref="C135:D135"/>
+    <mergeCell ref="C134:D134"/>
+    <mergeCell ref="G133:H133"/>
+    <mergeCell ref="F124:H124"/>
     <mergeCell ref="G138:H138"/>
-    <mergeCell ref="F128:H128"/>
-    <mergeCell ref="G143:H143"/>
-    <mergeCell ref="G144:H144"/>
-    <mergeCell ref="G141:H141"/>
-    <mergeCell ref="G142:H142"/>
-    <mergeCell ref="F129:F136"/>
+    <mergeCell ref="G139:H139"/>
+    <mergeCell ref="G136:H136"/>
+    <mergeCell ref="G137:H137"/>
+    <mergeCell ref="F125:F131"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
